--- a/data/sample_estate_demand.xlsx
+++ b/data/sample_estate_demand.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,13 +27,23 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -48,9 +58,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,191 +431,163 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:R29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="G1" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>Oct-26</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>Nov-26</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>Dec-26</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>September</t>
+          <t>Jan-27</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>September</t>
+          <t>Feb-27</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>September</t>
+          <t>Mar-27</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>September</t>
+          <t>Apr-27</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>October</t>
+          <t>May-27</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>October</t>
+          <t>Jun-27</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>October</t>
+          <t>Jul-27</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>October</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>November</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>November</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>November</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>November</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>November</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>December</t>
+          <t>Aug-27</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Account</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>LOB</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>Site</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="G2" s="1" t="n">
-        <v>46244</v>
-      </c>
-      <c r="H2" s="1" t="n">
-        <v>46251</v>
-      </c>
-      <c r="I2" s="1" t="n">
-        <v>46258</v>
-      </c>
-      <c r="J2" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="K2" s="1" t="n">
-        <v>46272</v>
-      </c>
-      <c r="L2" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="M2" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="N2" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="O2" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="P2" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="Q2" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="R2" s="1" t="n">
-        <v>46321</v>
-      </c>
-      <c r="S2" s="1" t="n">
-        <v>46328</v>
-      </c>
-      <c r="T2" s="1" t="n">
-        <v>46335</v>
-      </c>
-      <c r="U2" s="1" t="n">
-        <v>46342</v>
-      </c>
-      <c r="V2" s="1" t="n">
-        <v>46349</v>
-      </c>
-      <c r="W2" s="1" t="n">
-        <v>46356</v>
-      </c>
-      <c r="X2" s="1" t="n">
-        <v>46363</v>
+      <c r="G2" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>46327</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>46357</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>46388</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>46419</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>46447</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>46478</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>46508</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>46539</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>46569</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>46600</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TNS</t>
+          <t>Helio</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -610,17 +597,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bali</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bali</t>
+          <t>Aurora Park</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -629,64 +616,46 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>900</v>
+        <v>147</v>
       </c>
       <c r="H3" t="n">
-        <v>911</v>
+        <v>148</v>
       </c>
       <c r="I3" t="n">
-        <v>922</v>
+        <v>149</v>
       </c>
       <c r="J3" t="n">
-        <v>932</v>
+        <v>151</v>
       </c>
       <c r="K3" t="n">
-        <v>943</v>
+        <v>152</v>
       </c>
       <c r="L3" t="n">
-        <v>954</v>
+        <v>153</v>
       </c>
       <c r="M3" t="n">
-        <v>965</v>
+        <v>154</v>
       </c>
       <c r="N3" t="n">
-        <v>976</v>
+        <v>156</v>
       </c>
       <c r="O3" t="n">
-        <v>986</v>
+        <v>157</v>
       </c>
       <c r="P3" t="n">
-        <v>997</v>
+        <v>158</v>
       </c>
       <c r="Q3" t="n">
-        <v>1008</v>
+        <v>159</v>
       </c>
       <c r="R3" t="n">
-        <v>1019</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1030</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1040</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1051</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1062</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1073</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1084</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TNS</t>
+          <t>Helio</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -696,17 +665,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bali</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bali</t>
+          <t>Aurora Park</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -715,64 +684,46 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="M4" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="N4" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="P4" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TNS</t>
+          <t>Helio</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -782,17 +733,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bali</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bali</t>
+          <t>Aurora Park</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -801,84 +752,66 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>750</v>
+        <v>127.8</v>
       </c>
       <c r="H5" t="n">
-        <v>759.17</v>
+        <v>128.7</v>
       </c>
       <c r="I5" t="n">
-        <v>768.33</v>
+        <v>129.6</v>
       </c>
       <c r="J5" t="n">
-        <v>776.67</v>
+        <v>131.3</v>
       </c>
       <c r="K5" t="n">
-        <v>785.83</v>
+        <v>132.2</v>
       </c>
       <c r="L5" t="n">
-        <v>795</v>
+        <v>133</v>
       </c>
       <c r="M5" t="n">
-        <v>804.17</v>
+        <v>133.9</v>
       </c>
       <c r="N5" t="n">
-        <v>813.33</v>
+        <v>135.7</v>
       </c>
       <c r="O5" t="n">
-        <v>821.67</v>
+        <v>136.5</v>
       </c>
       <c r="P5" t="n">
-        <v>830.83</v>
+        <v>137.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>840</v>
+        <v>138.3</v>
       </c>
       <c r="R5" t="n">
-        <v>849.17</v>
-      </c>
-      <c r="S5" t="n">
-        <v>858.33</v>
-      </c>
-      <c r="T5" t="n">
-        <v>866.67</v>
-      </c>
-      <c r="U5" t="n">
-        <v>875.83</v>
-      </c>
-      <c r="V5" t="n">
-        <v>885</v>
-      </c>
-      <c r="W5" t="n">
-        <v>894.17</v>
-      </c>
-      <c r="X5" t="n">
-        <v>903.33</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>Vector</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Customer Care</t>
+          <t>Back Office</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bali</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bali</t>
+          <t>Aurora Park</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -887,84 +820,66 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>240</v>
+        <v>105</v>
       </c>
       <c r="H6" t="n">
-        <v>243</v>
+        <v>106</v>
       </c>
       <c r="I6" t="n">
-        <v>246</v>
+        <v>107</v>
       </c>
       <c r="J6" t="n">
-        <v>249</v>
+        <v>108</v>
       </c>
       <c r="K6" t="n">
-        <v>252</v>
+        <v>109</v>
       </c>
       <c r="L6" t="n">
-        <v>254</v>
+        <v>109</v>
       </c>
       <c r="M6" t="n">
-        <v>257</v>
+        <v>110</v>
       </c>
       <c r="N6" t="n">
-        <v>260</v>
+        <v>111</v>
       </c>
       <c r="O6" t="n">
-        <v>263</v>
+        <v>112</v>
       </c>
       <c r="P6" t="n">
-        <v>266</v>
+        <v>113</v>
       </c>
       <c r="Q6" t="n">
-        <v>269</v>
+        <v>114</v>
       </c>
       <c r="R6" t="n">
-        <v>272</v>
-      </c>
-      <c r="S6" t="n">
-        <v>275</v>
-      </c>
-      <c r="T6" t="n">
-        <v>277</v>
-      </c>
-      <c r="U6" t="n">
-        <v>280</v>
-      </c>
-      <c r="V6" t="n">
-        <v>283</v>
-      </c>
-      <c r="W6" t="n">
-        <v>286</v>
-      </c>
-      <c r="X6" t="n">
-        <v>289</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>Vector</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Customer Care</t>
+          <t>Back Office</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bali</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bali</t>
+          <t>Aurora Park</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -973,84 +888,66 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K7" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="M7" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="P7" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>Vector</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Customer Care</t>
+          <t>Back Office</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Bali</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bali</t>
+          <t>Aurora Park</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1059,84 +956,66 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>200</v>
+        <v>95.5</v>
       </c>
       <c r="H8" t="n">
-        <v>202.5</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>205</v>
+        <v>97.3</v>
       </c>
       <c r="J8" t="n">
-        <v>207.5</v>
+        <v>98.2</v>
       </c>
       <c r="K8" t="n">
-        <v>210</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>211.67</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>214.17</v>
+        <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>216.67</v>
+        <v>100.9</v>
       </c>
       <c r="O8" t="n">
-        <v>219.17</v>
+        <v>101.8</v>
       </c>
       <c r="P8" t="n">
-        <v>221.67</v>
+        <v>102.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>224.17</v>
+        <v>103.6</v>
       </c>
       <c r="R8" t="n">
-        <v>226.67</v>
-      </c>
-      <c r="S8" t="n">
-        <v>229.17</v>
-      </c>
-      <c r="T8" t="n">
-        <v>230.83</v>
-      </c>
-      <c r="U8" t="n">
-        <v>233.33</v>
-      </c>
-      <c r="V8" t="n">
-        <v>235.83</v>
-      </c>
-      <c r="W8" t="n">
-        <v>238.33</v>
-      </c>
-      <c r="X8" t="n">
-        <v>240.83</v>
+        <v>104.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TNS</t>
+          <t>Nimbus</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Billing</t>
+          <t>Escalations</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Surabaya</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Surabaya</t>
+          <t>Aurora Park</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1145,84 +1024,66 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="H9" t="n">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="I9" t="n">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="J9" t="n">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="K9" t="n">
-        <v>157</v>
+        <v>78</v>
       </c>
       <c r="L9" t="n">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="M9" t="n">
-        <v>161</v>
+        <v>79</v>
       </c>
       <c r="N9" t="n">
-        <v>163</v>
+        <v>80</v>
       </c>
       <c r="O9" t="n">
-        <v>164</v>
+        <v>81</v>
       </c>
       <c r="P9" t="n">
-        <v>166</v>
+        <v>81</v>
       </c>
       <c r="Q9" t="n">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="R9" t="n">
-        <v>170</v>
-      </c>
-      <c r="S9" t="n">
-        <v>172</v>
-      </c>
-      <c r="T9" t="n">
-        <v>173</v>
-      </c>
-      <c r="U9" t="n">
-        <v>175</v>
-      </c>
-      <c r="V9" t="n">
-        <v>177</v>
-      </c>
-      <c r="W9" t="n">
-        <v>179</v>
-      </c>
-      <c r="X9" t="n">
-        <v>181</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TNS</t>
+          <t>Nimbus</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Billing</t>
+          <t>Escalations</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Surabaya</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Surabaya</t>
+          <t>Aurora Park</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1231,84 +1092,66 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="K10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="M10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="N10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TNS</t>
+          <t>Nimbus</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Billing</t>
+          <t>Escalations</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Surabaya</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Surabaya</t>
+          <t>Aurora Park</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1317,84 +1160,66 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>115.38</v>
+        <v>60</v>
       </c>
       <c r="H11" t="n">
-        <v>116.92</v>
+        <v>60.8</v>
       </c>
       <c r="I11" t="n">
-        <v>118.46</v>
+        <v>60.8</v>
       </c>
       <c r="J11" t="n">
-        <v>119.23</v>
+        <v>61.6</v>
       </c>
       <c r="K11" t="n">
-        <v>120.77</v>
+        <v>62.4</v>
       </c>
       <c r="L11" t="n">
-        <v>122.31</v>
+        <v>63.2</v>
       </c>
       <c r="M11" t="n">
-        <v>123.85</v>
+        <v>63.2</v>
       </c>
       <c r="N11" t="n">
-        <v>125.38</v>
+        <v>64</v>
       </c>
       <c r="O11" t="n">
-        <v>126.15</v>
+        <v>64.8</v>
       </c>
       <c r="P11" t="n">
-        <v>127.69</v>
+        <v>64.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>129.23</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>130.77</v>
-      </c>
-      <c r="S11" t="n">
-        <v>132.31</v>
-      </c>
-      <c r="T11" t="n">
-        <v>133.08</v>
-      </c>
-      <c r="U11" t="n">
-        <v>134.62</v>
-      </c>
-      <c r="V11" t="n">
-        <v>136.15</v>
-      </c>
-      <c r="W11" t="n">
-        <v>137.69</v>
-      </c>
-      <c r="X11" t="n">
-        <v>139.23</v>
+        <v>66.40000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TNS</t>
+          <t>Vector</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Customer Care</t>
+          <t>Back Office</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Meridian One</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1403,84 +1228,66 @@
         </is>
       </c>
       <c r="G12" t="n">
+        <v>620</v>
+      </c>
+      <c r="H12" t="n">
+        <v>630</v>
+      </c>
+      <c r="I12" t="n">
         <v>640</v>
       </c>
-      <c r="H12" t="n">
-        <v>648</v>
-      </c>
-      <c r="I12" t="n">
-        <v>655</v>
-      </c>
       <c r="J12" t="n">
-        <v>663</v>
+        <v>650</v>
       </c>
       <c r="K12" t="n">
-        <v>671</v>
+        <v>660</v>
       </c>
       <c r="L12" t="n">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="M12" t="n">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="N12" t="n">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="O12" t="n">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="P12" t="n">
         <v>709</v>
       </c>
       <c r="Q12" t="n">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="R12" t="n">
-        <v>724</v>
-      </c>
-      <c r="S12" t="n">
-        <v>732</v>
-      </c>
-      <c r="T12" t="n">
-        <v>740</v>
-      </c>
-      <c r="U12" t="n">
-        <v>748</v>
-      </c>
-      <c r="V12" t="n">
-        <v>755</v>
-      </c>
-      <c r="W12" t="n">
-        <v>763</v>
-      </c>
-      <c r="X12" t="n">
-        <v>771</v>
+        <v>729</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TNS</t>
+          <t>Vector</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Customer Care</t>
+          <t>Back Office</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Meridian One</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1524,49 +1331,31 @@
       <c r="R13" t="n">
         <v>1.1</v>
       </c>
-      <c r="S13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TNS</t>
+          <t>Vector</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Customer Care</t>
+          <t>Back Office</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Meridian One</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1575,64 +1364,46 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>581.8200000000001</v>
+        <v>563.6</v>
       </c>
       <c r="H14" t="n">
-        <v>589.09</v>
+        <v>572.7</v>
       </c>
       <c r="I14" t="n">
-        <v>595.45</v>
+        <v>581.8</v>
       </c>
       <c r="J14" t="n">
-        <v>602.73</v>
+        <v>590.9</v>
       </c>
       <c r="K14" t="n">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="L14" t="n">
-        <v>616.36</v>
+        <v>609.1</v>
       </c>
       <c r="M14" t="n">
-        <v>623.64</v>
+        <v>618.2</v>
       </c>
       <c r="N14" t="n">
-        <v>630.91</v>
+        <v>626.4</v>
       </c>
       <c r="O14" t="n">
-        <v>637.27</v>
+        <v>635.5</v>
       </c>
       <c r="P14" t="n">
-        <v>644.55</v>
+        <v>644.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>651.8200000000001</v>
+        <v>653.6</v>
       </c>
       <c r="R14" t="n">
-        <v>658.1799999999999</v>
-      </c>
-      <c r="S14" t="n">
-        <v>665.45</v>
-      </c>
-      <c r="T14" t="n">
-        <v>672.73</v>
-      </c>
-      <c r="U14" t="n">
-        <v>680</v>
-      </c>
-      <c r="V14" t="n">
-        <v>686.36</v>
-      </c>
-      <c r="W14" t="n">
-        <v>693.64</v>
-      </c>
-      <c r="X14" t="n">
-        <v>700.91</v>
+        <v>662.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>Helio</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1642,17 +1413,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Skyline Center</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1661,64 +1432,46 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>160</v>
+        <v>560</v>
       </c>
       <c r="H15" t="n">
-        <v>162</v>
+        <v>575</v>
       </c>
       <c r="I15" t="n">
-        <v>164</v>
+        <v>589</v>
       </c>
       <c r="J15" t="n">
-        <v>166</v>
+        <v>604</v>
       </c>
       <c r="K15" t="n">
-        <v>168</v>
+        <v>618</v>
       </c>
       <c r="L15" t="n">
-        <v>170</v>
+        <v>633</v>
       </c>
       <c r="M15" t="n">
-        <v>172</v>
+        <v>647</v>
       </c>
       <c r="N15" t="n">
-        <v>173</v>
+        <v>662</v>
       </c>
       <c r="O15" t="n">
-        <v>175</v>
+        <v>676</v>
       </c>
       <c r="P15" t="n">
-        <v>177</v>
+        <v>691</v>
       </c>
       <c r="Q15" t="n">
-        <v>179</v>
+        <v>706</v>
       </c>
       <c r="R15" t="n">
-        <v>181</v>
-      </c>
-      <c r="S15" t="n">
-        <v>183</v>
-      </c>
-      <c r="T15" t="n">
-        <v>185</v>
-      </c>
-      <c r="U15" t="n">
-        <v>187</v>
-      </c>
-      <c r="V15" t="n">
-        <v>189</v>
-      </c>
-      <c r="W15" t="n">
-        <v>191</v>
-      </c>
-      <c r="X15" t="n">
-        <v>193</v>
+        <v>720</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>Helio</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1728,17 +1481,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Skyline Center</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1747,64 +1500,46 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="N16" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="O16" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>Helio</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1814,17 +1549,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Skyline Center</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1833,64 +1568,46 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>145.45</v>
+        <v>466.7</v>
       </c>
       <c r="H17" t="n">
-        <v>147.27</v>
+        <v>479.2</v>
       </c>
       <c r="I17" t="n">
-        <v>149.09</v>
+        <v>490.8</v>
       </c>
       <c r="J17" t="n">
-        <v>150.91</v>
+        <v>503.3</v>
       </c>
       <c r="K17" t="n">
-        <v>152.73</v>
+        <v>515</v>
       </c>
       <c r="L17" t="n">
-        <v>154.55</v>
+        <v>527.5</v>
       </c>
       <c r="M17" t="n">
-        <v>156.36</v>
+        <v>539.2</v>
       </c>
       <c r="N17" t="n">
-        <v>157.27</v>
+        <v>551.7</v>
       </c>
       <c r="O17" t="n">
-        <v>159.09</v>
+        <v>563.3</v>
       </c>
       <c r="P17" t="n">
-        <v>160.91</v>
+        <v>575.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>162.73</v>
+        <v>588.3</v>
       </c>
       <c r="R17" t="n">
-        <v>164.55</v>
-      </c>
-      <c r="S17" t="n">
-        <v>166.36</v>
-      </c>
-      <c r="T17" t="n">
-        <v>168.18</v>
-      </c>
-      <c r="U17" t="n">
-        <v>170</v>
-      </c>
-      <c r="V17" t="n">
-        <v>171.82</v>
-      </c>
-      <c r="W17" t="n">
-        <v>173.64</v>
-      </c>
-      <c r="X17" t="n">
-        <v>175.45</v>
+        <v>600</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V2</t>
+          <t>Nimbus</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1900,17 +1617,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Hanoi</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hanoi</t>
+          <t>Skyline Center</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1919,64 +1636,46 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>230</v>
+        <v>640</v>
       </c>
       <c r="H18" t="n">
-        <v>233</v>
+        <v>659</v>
       </c>
       <c r="I18" t="n">
-        <v>236</v>
+        <v>678</v>
       </c>
       <c r="J18" t="n">
-        <v>238</v>
+        <v>698</v>
       </c>
       <c r="K18" t="n">
-        <v>241</v>
+        <v>717</v>
       </c>
       <c r="L18" t="n">
-        <v>244</v>
+        <v>736</v>
       </c>
       <c r="M18" t="n">
-        <v>247</v>
+        <v>755</v>
       </c>
       <c r="N18" t="n">
-        <v>249</v>
+        <v>774</v>
       </c>
       <c r="O18" t="n">
-        <v>252</v>
+        <v>794</v>
       </c>
       <c r="P18" t="n">
-        <v>255</v>
+        <v>813</v>
       </c>
       <c r="Q18" t="n">
-        <v>258</v>
+        <v>832</v>
       </c>
       <c r="R18" t="n">
-        <v>260</v>
-      </c>
-      <c r="S18" t="n">
-        <v>263</v>
-      </c>
-      <c r="T18" t="n">
-        <v>266</v>
-      </c>
-      <c r="U18" t="n">
-        <v>269</v>
-      </c>
-      <c r="V18" t="n">
-        <v>271</v>
-      </c>
-      <c r="W18" t="n">
-        <v>274</v>
-      </c>
-      <c r="X18" t="n">
-        <v>277</v>
+        <v>851</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V2</t>
+          <t>Nimbus</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1986,17 +1685,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Hanoi</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hanoi</t>
+          <t>Skyline Center</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2038,31 +1737,13 @@
         <v>1.2</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X19" t="n">
         <v>1.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V2</t>
+          <t>Nimbus</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2072,17 +1753,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Hanoi</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hanoi</t>
+          <t>Skyline Center</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2091,64 +1772,46 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>191.67</v>
+        <v>533.3</v>
       </c>
       <c r="H20" t="n">
-        <v>194.17</v>
+        <v>549.2</v>
       </c>
       <c r="I20" t="n">
-        <v>196.67</v>
+        <v>565</v>
       </c>
       <c r="J20" t="n">
-        <v>198.33</v>
+        <v>581.7</v>
       </c>
       <c r="K20" t="n">
-        <v>200.83</v>
+        <v>597.5</v>
       </c>
       <c r="L20" t="n">
-        <v>203.33</v>
+        <v>613.3</v>
       </c>
       <c r="M20" t="n">
-        <v>205.83</v>
+        <v>629.2</v>
       </c>
       <c r="N20" t="n">
-        <v>207.5</v>
+        <v>645</v>
       </c>
       <c r="O20" t="n">
-        <v>210</v>
+        <v>661.7</v>
       </c>
       <c r="P20" t="n">
-        <v>212.5</v>
+        <v>677.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>215</v>
+        <v>693.3</v>
       </c>
       <c r="R20" t="n">
-        <v>216.67</v>
-      </c>
-      <c r="S20" t="n">
-        <v>219.17</v>
-      </c>
-      <c r="T20" t="n">
-        <v>221.67</v>
-      </c>
-      <c r="U20" t="n">
-        <v>224.17</v>
-      </c>
-      <c r="V20" t="n">
-        <v>225.83</v>
-      </c>
-      <c r="W20" t="n">
-        <v>228.33</v>
-      </c>
-      <c r="X20" t="n">
-        <v>230.83</v>
+        <v>709.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TNS</t>
+          <t>Nimbus</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2158,17 +1821,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Danang</t>
+          <t>Cebu</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Danang</t>
+          <t>Harbour Point</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2177,64 +1840,46 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>520</v>
+        <v>230</v>
       </c>
       <c r="H21" t="n">
-        <v>526</v>
+        <v>234</v>
       </c>
       <c r="I21" t="n">
-        <v>532</v>
+        <v>238</v>
       </c>
       <c r="J21" t="n">
-        <v>539</v>
+        <v>242</v>
       </c>
       <c r="K21" t="n">
-        <v>545</v>
+        <v>247</v>
       </c>
       <c r="L21" t="n">
-        <v>551</v>
+        <v>251</v>
       </c>
       <c r="M21" t="n">
-        <v>557</v>
+        <v>255</v>
       </c>
       <c r="N21" t="n">
-        <v>564</v>
+        <v>259</v>
       </c>
       <c r="O21" t="n">
-        <v>570</v>
+        <v>263</v>
       </c>
       <c r="P21" t="n">
-        <v>576</v>
+        <v>267</v>
       </c>
       <c r="Q21" t="n">
-        <v>582</v>
+        <v>271</v>
       </c>
       <c r="R21" t="n">
-        <v>589</v>
-      </c>
-      <c r="S21" t="n">
-        <v>595</v>
-      </c>
-      <c r="T21" t="n">
-        <v>601</v>
-      </c>
-      <c r="U21" t="n">
-        <v>607</v>
-      </c>
-      <c r="V21" t="n">
-        <v>614</v>
-      </c>
-      <c r="W21" t="n">
-        <v>620</v>
-      </c>
-      <c r="X21" t="n">
-        <v>626</v>
+        <v>276</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TNS</t>
+          <t>Nimbus</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2244,17 +1889,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Danang</t>
+          <t>Cebu</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Danang</t>
+          <t>Harbour Point</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2296,31 +1941,13 @@
         <v>1.2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X22" t="n">
         <v>1.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TNS</t>
+          <t>Nimbus</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2330,17 +1957,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Danang</t>
+          <t>Cebu</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Danang</t>
+          <t>Harbour Point</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2349,84 +1976,66 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>433.33</v>
+        <v>191.7</v>
       </c>
       <c r="H23" t="n">
-        <v>438.33</v>
+        <v>195</v>
       </c>
       <c r="I23" t="n">
-        <v>443.33</v>
+        <v>198.3</v>
       </c>
       <c r="J23" t="n">
-        <v>449.17</v>
+        <v>201.7</v>
       </c>
       <c r="K23" t="n">
-        <v>454.17</v>
+        <v>205.8</v>
       </c>
       <c r="L23" t="n">
-        <v>459.17</v>
+        <v>209.2</v>
       </c>
       <c r="M23" t="n">
-        <v>464.17</v>
+        <v>212.5</v>
       </c>
       <c r="N23" t="n">
-        <v>470</v>
+        <v>215.8</v>
       </c>
       <c r="O23" t="n">
-        <v>475</v>
+        <v>219.2</v>
       </c>
       <c r="P23" t="n">
-        <v>480</v>
+        <v>222.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>485</v>
+        <v>225.8</v>
       </c>
       <c r="R23" t="n">
-        <v>490.83</v>
-      </c>
-      <c r="S23" t="n">
-        <v>495.83</v>
-      </c>
-      <c r="T23" t="n">
-        <v>500.83</v>
-      </c>
-      <c r="U23" t="n">
-        <v>505.83</v>
-      </c>
-      <c r="V23" t="n">
-        <v>511.67</v>
-      </c>
-      <c r="W23" t="n">
-        <v>516.67</v>
-      </c>
-      <c r="X23" t="n">
-        <v>521.67</v>
+        <v>230</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TNS</t>
+          <t>Vector</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Back Office</t>
+          <t>Collections</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Krakow</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Vistula House</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2435,84 +2044,66 @@
         </is>
       </c>
       <c r="G24" t="n">
+        <v>300</v>
+      </c>
+      <c r="H24" t="n">
+        <v>306</v>
+      </c>
+      <c r="I24" t="n">
+        <v>312</v>
+      </c>
+      <c r="J24" t="n">
+        <v>318</v>
+      </c>
+      <c r="K24" t="n">
+        <v>324</v>
+      </c>
+      <c r="L24" t="n">
         <v>330</v>
       </c>
-      <c r="H24" t="n">
-        <v>334</v>
-      </c>
-      <c r="I24" t="n">
-        <v>338</v>
-      </c>
-      <c r="J24" t="n">
+      <c r="M24" t="n">
+        <v>336</v>
+      </c>
+      <c r="N24" t="n">
         <v>342</v>
       </c>
-      <c r="K24" t="n">
-        <v>346</v>
-      </c>
-      <c r="L24" t="n">
-        <v>350</v>
-      </c>
-      <c r="M24" t="n">
+      <c r="O24" t="n">
+        <v>348</v>
+      </c>
+      <c r="P24" t="n">
         <v>354</v>
       </c>
-      <c r="N24" t="n">
-        <v>358</v>
-      </c>
-      <c r="O24" t="n">
-        <v>362</v>
-      </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
+        <v>360</v>
+      </c>
+      <c r="R24" t="n">
         <v>366</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>370</v>
-      </c>
-      <c r="R24" t="n">
-        <v>374</v>
-      </c>
-      <c r="S24" t="n">
-        <v>378</v>
-      </c>
-      <c r="T24" t="n">
-        <v>381</v>
-      </c>
-      <c r="U24" t="n">
-        <v>385</v>
-      </c>
-      <c r="V24" t="n">
-        <v>389</v>
-      </c>
-      <c r="W24" t="n">
-        <v>393</v>
-      </c>
-      <c r="X24" t="n">
-        <v>397</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TNS</t>
+          <t>Vector</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Back Office</t>
+          <t>Collections</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Krakow</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Vistula House</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2521,84 +2112,66 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="O25" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="P25" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TNS</t>
+          <t>Vector</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Back Office</t>
+          <t>Collections</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Krakow</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Vistula House</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2607,58 +2180,244 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>330</v>
+        <v>240</v>
       </c>
       <c r="H26" t="n">
-        <v>334</v>
+        <v>244.8</v>
       </c>
       <c r="I26" t="n">
-        <v>338</v>
+        <v>249.6</v>
       </c>
       <c r="J26" t="n">
-        <v>342</v>
+        <v>254.4</v>
       </c>
       <c r="K26" t="n">
-        <v>346</v>
+        <v>259.2</v>
       </c>
       <c r="L26" t="n">
-        <v>350</v>
+        <v>264</v>
       </c>
       <c r="M26" t="n">
-        <v>354</v>
+        <v>268.8</v>
       </c>
       <c r="N26" t="n">
-        <v>358</v>
+        <v>273.6</v>
       </c>
       <c r="O26" t="n">
-        <v>362</v>
+        <v>278.4</v>
       </c>
       <c r="P26" t="n">
-        <v>366</v>
+        <v>283.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>370</v>
+        <v>288</v>
       </c>
       <c r="R26" t="n">
-        <v>374</v>
-      </c>
-      <c r="S26" t="n">
-        <v>378</v>
-      </c>
-      <c r="T26" t="n">
-        <v>381</v>
-      </c>
-      <c r="U26" t="n">
-        <v>385</v>
-      </c>
-      <c r="V26" t="n">
-        <v>389</v>
-      </c>
-      <c r="W26" t="n">
-        <v>393</v>
-      </c>
-      <c r="X26" t="n">
-        <v>397</v>
+        <v>292.8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Nimbus</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Escalations</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Krakow</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Vistula House</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>HC Forecast</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>95</v>
+      </c>
+      <c r="H27" t="n">
+        <v>96</v>
+      </c>
+      <c r="I27" t="n">
+        <v>98</v>
+      </c>
+      <c r="J27" t="n">
+        <v>99</v>
+      </c>
+      <c r="K27" t="n">
+        <v>100</v>
+      </c>
+      <c r="L27" t="n">
+        <v>102</v>
+      </c>
+      <c r="M27" t="n">
+        <v>103</v>
+      </c>
+      <c r="N27" t="n">
+        <v>104</v>
+      </c>
+      <c r="O27" t="n">
+        <v>106</v>
+      </c>
+      <c r="P27" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>108</v>
+      </c>
+      <c r="R27" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Nimbus</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Escalations</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Krakow</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Vistula House</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Seat Ratio</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Nimbus</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Escalations</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Krakow</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Vistula House</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Seats Required</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>76</v>
+      </c>
+      <c r="H29" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="I29" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="J29" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="K29" t="n">
+        <v>80</v>
+      </c>
+      <c r="L29" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="M29" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="N29" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="O29" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="P29" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="R29" t="n">
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/data/sample_estate_demand.xlsx
+++ b/data/sample_estate_demand.xlsx
@@ -431,27 +431,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R29"/>
+  <dimension ref="A1:R128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -587,7 +575,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Helio</t>
+          <t>Client A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -597,17 +585,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aurora Park</t>
+          <t>APA-MNL-01</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -616,46 +604,46 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>147</v>
+        <v>590</v>
       </c>
       <c r="H3" t="n">
-        <v>148</v>
+        <v>608</v>
       </c>
       <c r="I3" t="n">
-        <v>149</v>
+        <v>626</v>
       </c>
       <c r="J3" t="n">
-        <v>151</v>
+        <v>643</v>
       </c>
       <c r="K3" t="n">
-        <v>152</v>
+        <v>661</v>
       </c>
       <c r="L3" t="n">
-        <v>153</v>
+        <v>679</v>
       </c>
       <c r="M3" t="n">
-        <v>154</v>
+        <v>697</v>
       </c>
       <c r="N3" t="n">
-        <v>156</v>
+        <v>714</v>
       </c>
       <c r="O3" t="n">
-        <v>157</v>
+        <v>732</v>
       </c>
       <c r="P3" t="n">
-        <v>158</v>
+        <v>750</v>
       </c>
       <c r="Q3" t="n">
-        <v>159</v>
+        <v>767</v>
       </c>
       <c r="R3" t="n">
-        <v>161</v>
+        <v>785</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Helio</t>
+          <t>Client A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -665,17 +653,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aurora Park</t>
+          <t>APA-MNL-01</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -723,7 +711,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Helio</t>
+          <t>Client A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -733,17 +721,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aurora Park</t>
+          <t>APA-MNL-01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -752,66 +740,66 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>127.8</v>
+        <v>513</v>
       </c>
       <c r="H5" t="n">
-        <v>128.7</v>
+        <v>528.7</v>
       </c>
       <c r="I5" t="n">
-        <v>129.6</v>
+        <v>544.3</v>
       </c>
       <c r="J5" t="n">
-        <v>131.3</v>
+        <v>559.1</v>
       </c>
       <c r="K5" t="n">
-        <v>132.2</v>
+        <v>574.8</v>
       </c>
       <c r="L5" t="n">
-        <v>133</v>
+        <v>590.4</v>
       </c>
       <c r="M5" t="n">
-        <v>133.9</v>
+        <v>606.1</v>
       </c>
       <c r="N5" t="n">
-        <v>135.7</v>
+        <v>620.9</v>
       </c>
       <c r="O5" t="n">
-        <v>136.5</v>
+        <v>636.5</v>
       </c>
       <c r="P5" t="n">
-        <v>137.4</v>
+        <v>652.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>138.3</v>
+        <v>667</v>
       </c>
       <c r="R5" t="n">
-        <v>140</v>
+        <v>682.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Client B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Back Office</t>
+          <t>Tech Support</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aurora Park</t>
+          <t>APA-MNL-01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -820,66 +808,66 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>105</v>
+        <v>393</v>
       </c>
       <c r="H6" t="n">
-        <v>106</v>
+        <v>405</v>
       </c>
       <c r="I6" t="n">
-        <v>107</v>
+        <v>417</v>
       </c>
       <c r="J6" t="n">
-        <v>108</v>
+        <v>429</v>
       </c>
       <c r="K6" t="n">
-        <v>109</v>
+        <v>440</v>
       </c>
       <c r="L6" t="n">
-        <v>109</v>
+        <v>452</v>
       </c>
       <c r="M6" t="n">
-        <v>110</v>
+        <v>464</v>
       </c>
       <c r="N6" t="n">
-        <v>111</v>
+        <v>476</v>
       </c>
       <c r="O6" t="n">
-        <v>112</v>
+        <v>488</v>
       </c>
       <c r="P6" t="n">
-        <v>113</v>
+        <v>499</v>
       </c>
       <c r="Q6" t="n">
-        <v>114</v>
+        <v>511</v>
       </c>
       <c r="R6" t="n">
-        <v>115</v>
+        <v>523</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Client B</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Back Office</t>
+          <t>Tech Support</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aurora Park</t>
+          <t>APA-MNL-01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -888,66 +876,66 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="L7" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="N7" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Client B</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Back Office</t>
+          <t>Tech Support</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aurora Park</t>
+          <t>APA-MNL-01</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -956,66 +944,66 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>95.5</v>
+        <v>314.4</v>
       </c>
       <c r="H8" t="n">
-        <v>96.40000000000001</v>
+        <v>324</v>
       </c>
       <c r="I8" t="n">
-        <v>97.3</v>
+        <v>333.6</v>
       </c>
       <c r="J8" t="n">
-        <v>98.2</v>
+        <v>343.2</v>
       </c>
       <c r="K8" t="n">
-        <v>99.09999999999999</v>
+        <v>352</v>
       </c>
       <c r="L8" t="n">
-        <v>99.09999999999999</v>
+        <v>361.6</v>
       </c>
       <c r="M8" t="n">
-        <v>100</v>
+        <v>371.2</v>
       </c>
       <c r="N8" t="n">
-        <v>100.9</v>
+        <v>380.8</v>
       </c>
       <c r="O8" t="n">
-        <v>101.8</v>
+        <v>390.4</v>
       </c>
       <c r="P8" t="n">
-        <v>102.7</v>
+        <v>399.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>103.6</v>
+        <v>408.8</v>
       </c>
       <c r="R8" t="n">
-        <v>104.5</v>
+        <v>418.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nimbus</t>
+          <t>Client A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Escalations</t>
+          <t>Customer Care</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aurora Park</t>
+          <t>APA-MNL-02</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1024,66 +1012,66 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>75</v>
+        <v>224</v>
       </c>
       <c r="H9" t="n">
-        <v>76</v>
+        <v>227</v>
       </c>
       <c r="I9" t="n">
-        <v>76</v>
+        <v>229</v>
       </c>
       <c r="J9" t="n">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="K9" t="n">
-        <v>78</v>
+        <v>234</v>
       </c>
       <c r="L9" t="n">
-        <v>79</v>
+        <v>237</v>
       </c>
       <c r="M9" t="n">
-        <v>79</v>
+        <v>240</v>
       </c>
       <c r="N9" t="n">
-        <v>80</v>
+        <v>242</v>
       </c>
       <c r="O9" t="n">
-        <v>81</v>
+        <v>245</v>
       </c>
       <c r="P9" t="n">
-        <v>81</v>
+        <v>247</v>
       </c>
       <c r="Q9" t="n">
-        <v>82</v>
+        <v>250</v>
       </c>
       <c r="R9" t="n">
-        <v>83</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nimbus</t>
+          <t>Client A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Escalations</t>
+          <t>Customer Care</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aurora Park</t>
+          <t>APA-MNL-02</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1092,66 +1080,66 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="H10" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="I10" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="J10" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="K10" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="L10" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="M10" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="O10" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="P10" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nimbus</t>
+          <t>Client A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Escalations</t>
+          <t>Customer Care</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aurora Park</t>
+          <t>APA-MNL-02</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1160,66 +1148,66 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>60</v>
+        <v>194.8</v>
       </c>
       <c r="H11" t="n">
-        <v>60.8</v>
+        <v>197.4</v>
       </c>
       <c r="I11" t="n">
-        <v>60.8</v>
+        <v>199.1</v>
       </c>
       <c r="J11" t="n">
-        <v>61.6</v>
+        <v>201.7</v>
       </c>
       <c r="K11" t="n">
-        <v>62.4</v>
+        <v>203.5</v>
       </c>
       <c r="L11" t="n">
-        <v>63.2</v>
+        <v>206.1</v>
       </c>
       <c r="M11" t="n">
-        <v>63.2</v>
+        <v>208.7</v>
       </c>
       <c r="N11" t="n">
-        <v>64</v>
+        <v>210.4</v>
       </c>
       <c r="O11" t="n">
-        <v>64.8</v>
+        <v>213</v>
       </c>
       <c r="P11" t="n">
-        <v>64.8</v>
+        <v>214.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>65.59999999999999</v>
+        <v>217.4</v>
       </c>
       <c r="R11" t="n">
-        <v>66.40000000000001</v>
+        <v>219.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Client A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Back Office</t>
+          <t>Billing</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Meridian One</t>
+          <t>APA-MNL-02</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1228,66 +1216,66 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>620</v>
+        <v>224</v>
       </c>
       <c r="H12" t="n">
-        <v>630</v>
+        <v>227</v>
       </c>
       <c r="I12" t="n">
-        <v>640</v>
+        <v>229</v>
       </c>
       <c r="J12" t="n">
-        <v>650</v>
+        <v>232</v>
       </c>
       <c r="K12" t="n">
-        <v>660</v>
+        <v>234</v>
       </c>
       <c r="L12" t="n">
-        <v>670</v>
+        <v>237</v>
       </c>
       <c r="M12" t="n">
-        <v>680</v>
+        <v>240</v>
       </c>
       <c r="N12" t="n">
-        <v>689</v>
+        <v>242</v>
       </c>
       <c r="O12" t="n">
-        <v>699</v>
+        <v>245</v>
       </c>
       <c r="P12" t="n">
-        <v>709</v>
+        <v>247</v>
       </c>
       <c r="Q12" t="n">
-        <v>719</v>
+        <v>250</v>
       </c>
       <c r="R12" t="n">
-        <v>729</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Client A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Back Office</t>
+          <t>Billing</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Meridian One</t>
+          <t>APA-MNL-02</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1296,66 +1284,66 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="K13" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="L13" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="N13" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="O13" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Client A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Back Office</t>
+          <t>Billing</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Meridian One</t>
+          <t>APA-MNL-02</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1364,46 +1352,46 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>563.6</v>
+        <v>194.8</v>
       </c>
       <c r="H14" t="n">
-        <v>572.7</v>
+        <v>197.4</v>
       </c>
       <c r="I14" t="n">
-        <v>581.8</v>
+        <v>199.1</v>
       </c>
       <c r="J14" t="n">
-        <v>590.9</v>
+        <v>201.7</v>
       </c>
       <c r="K14" t="n">
-        <v>600</v>
+        <v>203.5</v>
       </c>
       <c r="L14" t="n">
-        <v>609.1</v>
+        <v>206.1</v>
       </c>
       <c r="M14" t="n">
-        <v>618.2</v>
+        <v>208.7</v>
       </c>
       <c r="N14" t="n">
-        <v>626.4</v>
+        <v>210.4</v>
       </c>
       <c r="O14" t="n">
-        <v>635.5</v>
+        <v>213</v>
       </c>
       <c r="P14" t="n">
-        <v>644.5</v>
+        <v>214.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>653.6</v>
+        <v>217.4</v>
       </c>
       <c r="R14" t="n">
-        <v>662.7</v>
+        <v>219.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Helio</t>
+          <t>Client B</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1413,17 +1401,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Manila</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Skyline Center</t>
+          <t>APA-BKK-01</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1432,46 +1420,46 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>560</v>
+        <v>266</v>
       </c>
       <c r="H15" t="n">
-        <v>575</v>
+        <v>269</v>
       </c>
       <c r="I15" t="n">
-        <v>589</v>
+        <v>272</v>
       </c>
       <c r="J15" t="n">
-        <v>604</v>
+        <v>276</v>
       </c>
       <c r="K15" t="n">
-        <v>618</v>
+        <v>279</v>
       </c>
       <c r="L15" t="n">
-        <v>633</v>
+        <v>282</v>
       </c>
       <c r="M15" t="n">
-        <v>647</v>
+        <v>286</v>
       </c>
       <c r="N15" t="n">
-        <v>662</v>
+        <v>289</v>
       </c>
       <c r="O15" t="n">
-        <v>676</v>
+        <v>292</v>
       </c>
       <c r="P15" t="n">
-        <v>691</v>
+        <v>296</v>
       </c>
       <c r="Q15" t="n">
-        <v>706</v>
+        <v>299</v>
       </c>
       <c r="R15" t="n">
-        <v>720</v>
+        <v>302</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Helio</t>
+          <t>Client B</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1481,17 +1469,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Manila</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Skyline Center</t>
+          <t>APA-BKK-01</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1500,46 +1488,46 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="M16" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="N16" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="O16" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="P16" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Helio</t>
+          <t>Client B</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1549,17 +1537,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Manila</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Skyline Center</t>
+          <t>APA-BKK-01</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1568,66 +1556,66 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>466.7</v>
+        <v>212.8</v>
       </c>
       <c r="H17" t="n">
-        <v>479.2</v>
+        <v>215.2</v>
       </c>
       <c r="I17" t="n">
-        <v>490.8</v>
+        <v>217.6</v>
       </c>
       <c r="J17" t="n">
-        <v>503.3</v>
+        <v>220.8</v>
       </c>
       <c r="K17" t="n">
-        <v>515</v>
+        <v>223.2</v>
       </c>
       <c r="L17" t="n">
-        <v>527.5</v>
+        <v>225.6</v>
       </c>
       <c r="M17" t="n">
-        <v>539.2</v>
+        <v>228.8</v>
       </c>
       <c r="N17" t="n">
-        <v>551.7</v>
+        <v>231.2</v>
       </c>
       <c r="O17" t="n">
-        <v>563.3</v>
+        <v>233.6</v>
       </c>
       <c r="P17" t="n">
-        <v>575.8</v>
+        <v>236.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>588.3</v>
+        <v>239.2</v>
       </c>
       <c r="R17" t="n">
-        <v>600</v>
+        <v>241.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nimbus</t>
+          <t>Client B</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Customer Care</t>
+          <t>Back Office</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Manila</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Skyline Center</t>
+          <t>APA-BKK-01</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1636,66 +1624,66 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>640</v>
+        <v>266</v>
       </c>
       <c r="H18" t="n">
-        <v>659</v>
+        <v>269</v>
       </c>
       <c r="I18" t="n">
-        <v>678</v>
+        <v>272</v>
       </c>
       <c r="J18" t="n">
-        <v>698</v>
+        <v>276</v>
       </c>
       <c r="K18" t="n">
-        <v>717</v>
+        <v>279</v>
       </c>
       <c r="L18" t="n">
-        <v>736</v>
+        <v>282</v>
       </c>
       <c r="M18" t="n">
-        <v>755</v>
+        <v>286</v>
       </c>
       <c r="N18" t="n">
-        <v>774</v>
+        <v>289</v>
       </c>
       <c r="O18" t="n">
-        <v>794</v>
+        <v>292</v>
       </c>
       <c r="P18" t="n">
-        <v>813</v>
+        <v>296</v>
       </c>
       <c r="Q18" t="n">
-        <v>832</v>
+        <v>299</v>
       </c>
       <c r="R18" t="n">
-        <v>851</v>
+        <v>302</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nimbus</t>
+          <t>Client B</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Customer Care</t>
+          <t>Back Office</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Manila</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Skyline Center</t>
+          <t>APA-BKK-01</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1704,66 +1692,66 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="K19" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="N19" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="O19" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="P19" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nimbus</t>
+          <t>Client B</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Customer Care</t>
+          <t>Back Office</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Manila</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Skyline Center</t>
+          <t>APA-BKK-01</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1772,66 +1760,66 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>533.3</v>
+        <v>212.8</v>
       </c>
       <c r="H20" t="n">
-        <v>549.2</v>
+        <v>215.2</v>
       </c>
       <c r="I20" t="n">
-        <v>565</v>
+        <v>217.6</v>
       </c>
       <c r="J20" t="n">
-        <v>581.7</v>
+        <v>220.8</v>
       </c>
       <c r="K20" t="n">
-        <v>597.5</v>
+        <v>223.2</v>
       </c>
       <c r="L20" t="n">
-        <v>613.3</v>
+        <v>225.6</v>
       </c>
       <c r="M20" t="n">
-        <v>629.2</v>
+        <v>228.8</v>
       </c>
       <c r="N20" t="n">
-        <v>645</v>
+        <v>231.2</v>
       </c>
       <c r="O20" t="n">
-        <v>661.7</v>
+        <v>233.6</v>
       </c>
       <c r="P20" t="n">
-        <v>677.5</v>
+        <v>236.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>693.3</v>
+        <v>239.2</v>
       </c>
       <c r="R20" t="n">
-        <v>709.2</v>
+        <v>241.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nimbus</t>
+          <t>Client B</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Customer Care</t>
+          <t>Tech Support</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cebu</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Harbour Point</t>
+          <t>APA-BKK-02</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1840,66 +1828,66 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>230</v>
+        <v>337</v>
       </c>
       <c r="H21" t="n">
-        <v>234</v>
+        <v>339</v>
       </c>
       <c r="I21" t="n">
-        <v>238</v>
+        <v>341</v>
       </c>
       <c r="J21" t="n">
-        <v>242</v>
+        <v>343</v>
       </c>
       <c r="K21" t="n">
-        <v>247</v>
+        <v>345</v>
       </c>
       <c r="L21" t="n">
-        <v>251</v>
+        <v>347</v>
       </c>
       <c r="M21" t="n">
-        <v>255</v>
+        <v>349</v>
       </c>
       <c r="N21" t="n">
-        <v>259</v>
+        <v>351</v>
       </c>
       <c r="O21" t="n">
-        <v>263</v>
+        <v>353</v>
       </c>
       <c r="P21" t="n">
-        <v>267</v>
+        <v>355</v>
       </c>
       <c r="Q21" t="n">
-        <v>271</v>
+        <v>357</v>
       </c>
       <c r="R21" t="n">
-        <v>276</v>
+        <v>359</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nimbus</t>
+          <t>Client B</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Customer Care</t>
+          <t>Tech Support</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cebu</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Harbour Point</t>
+          <t>APA-BKK-02</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1908,66 +1896,66 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="J22" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="K22" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="L22" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="M22" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="N22" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="O22" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="P22" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nimbus</t>
+          <t>Client B</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Customer Care</t>
+          <t>Tech Support</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cebu</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Harbour Point</t>
+          <t>APA-BKK-02</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1976,46 +1964,46 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>191.7</v>
+        <v>269.6</v>
       </c>
       <c r="H23" t="n">
-        <v>195</v>
+        <v>271.2</v>
       </c>
       <c r="I23" t="n">
-        <v>198.3</v>
+        <v>272.8</v>
       </c>
       <c r="J23" t="n">
-        <v>201.7</v>
+        <v>274.4</v>
       </c>
       <c r="K23" t="n">
-        <v>205.8</v>
+        <v>276</v>
       </c>
       <c r="L23" t="n">
-        <v>209.2</v>
+        <v>277.6</v>
       </c>
       <c r="M23" t="n">
-        <v>212.5</v>
+        <v>279.2</v>
       </c>
       <c r="N23" t="n">
-        <v>215.8</v>
+        <v>280.8</v>
       </c>
       <c r="O23" t="n">
-        <v>219.2</v>
+        <v>282.4</v>
       </c>
       <c r="P23" t="n">
-        <v>222.5</v>
+        <v>284</v>
       </c>
       <c r="Q23" t="n">
-        <v>225.8</v>
+        <v>285.6</v>
       </c>
       <c r="R23" t="n">
-        <v>230</v>
+        <v>287.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Client C</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2025,17 +2013,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Krakow</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vistula House</t>
+          <t>APA-BKK-02</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2044,46 +2032,46 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>300</v>
+        <v>182</v>
       </c>
       <c r="H24" t="n">
-        <v>306</v>
+        <v>183</v>
       </c>
       <c r="I24" t="n">
-        <v>312</v>
+        <v>184</v>
       </c>
       <c r="J24" t="n">
-        <v>318</v>
+        <v>185</v>
       </c>
       <c r="K24" t="n">
-        <v>324</v>
+        <v>186</v>
       </c>
       <c r="L24" t="n">
-        <v>330</v>
+        <v>187</v>
       </c>
       <c r="M24" t="n">
-        <v>336</v>
+        <v>188</v>
       </c>
       <c r="N24" t="n">
-        <v>342</v>
+        <v>189</v>
       </c>
       <c r="O24" t="n">
-        <v>348</v>
+        <v>191</v>
       </c>
       <c r="P24" t="n">
-        <v>354</v>
+        <v>192</v>
       </c>
       <c r="Q24" t="n">
-        <v>360</v>
+        <v>193</v>
       </c>
       <c r="R24" t="n">
-        <v>366</v>
+        <v>194</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Client C</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2093,17 +2081,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Krakow</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vistula House</t>
+          <t>APA-BKK-02</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2112,46 +2100,46 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="H25" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="I25" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="K25" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="L25" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="M25" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="N25" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O25" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="P25" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Client C</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2161,17 +2149,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Krakow</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vistula House</t>
+          <t>APA-BKK-02</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2180,66 +2168,66 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>240</v>
+        <v>165.5</v>
       </c>
       <c r="H26" t="n">
-        <v>244.8</v>
+        <v>166.4</v>
       </c>
       <c r="I26" t="n">
-        <v>249.6</v>
+        <v>167.3</v>
       </c>
       <c r="J26" t="n">
-        <v>254.4</v>
+        <v>168.2</v>
       </c>
       <c r="K26" t="n">
-        <v>259.2</v>
+        <v>169.1</v>
       </c>
       <c r="L26" t="n">
-        <v>264</v>
+        <v>170</v>
       </c>
       <c r="M26" t="n">
-        <v>268.8</v>
+        <v>170.9</v>
       </c>
       <c r="N26" t="n">
-        <v>273.6</v>
+        <v>171.8</v>
       </c>
       <c r="O26" t="n">
-        <v>278.4</v>
+        <v>173.6</v>
       </c>
       <c r="P26" t="n">
-        <v>283.2</v>
+        <v>174.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>288</v>
+        <v>175.5</v>
       </c>
       <c r="R26" t="n">
-        <v>292.8</v>
+        <v>176.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nimbus</t>
+          <t>Client A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Escalations</t>
+          <t>Customer Care</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Krakow</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vistula House</t>
+          <t>APA-MAA-01</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2248,66 +2236,66 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>95</v>
+        <v>535</v>
       </c>
       <c r="H27" t="n">
-        <v>96</v>
+        <v>545</v>
       </c>
       <c r="I27" t="n">
-        <v>98</v>
+        <v>555</v>
       </c>
       <c r="J27" t="n">
-        <v>99</v>
+        <v>564</v>
       </c>
       <c r="K27" t="n">
-        <v>100</v>
+        <v>574</v>
       </c>
       <c r="L27" t="n">
-        <v>102</v>
+        <v>584</v>
       </c>
       <c r="M27" t="n">
-        <v>103</v>
+        <v>593</v>
       </c>
       <c r="N27" t="n">
-        <v>104</v>
+        <v>603</v>
       </c>
       <c r="O27" t="n">
-        <v>106</v>
+        <v>612</v>
       </c>
       <c r="P27" t="n">
-        <v>107</v>
+        <v>622</v>
       </c>
       <c r="Q27" t="n">
-        <v>108</v>
+        <v>632</v>
       </c>
       <c r="R27" t="n">
-        <v>110</v>
+        <v>641</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nimbus</t>
+          <t>Client A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Escalations</t>
+          <t>Customer Care</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Krakow</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vistula House</t>
+          <t>APA-MAA-01</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2316,108 +2304,6840 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="H28" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="I28" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="J28" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="K28" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="L28" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="M28" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="N28" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="O28" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="P28" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="R28" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Nimbus</t>
+          <t>Client A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>Customer Care</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>APA-MAA-01</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Seats Required</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>465.2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>473.9</v>
+      </c>
+      <c r="I29" t="n">
+        <v>482.6</v>
+      </c>
+      <c r="J29" t="n">
+        <v>490.4</v>
+      </c>
+      <c r="K29" t="n">
+        <v>499.1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>507.8</v>
+      </c>
+      <c r="M29" t="n">
+        <v>515.7</v>
+      </c>
+      <c r="N29" t="n">
+        <v>524.3</v>
+      </c>
+      <c r="O29" t="n">
+        <v>532.2</v>
+      </c>
+      <c r="P29" t="n">
+        <v>540.9</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>549.6</v>
+      </c>
+      <c r="R29" t="n">
+        <v>557.4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Client A</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>APA-MAA-01</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>HC Forecast</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>535</v>
+      </c>
+      <c r="H30" t="n">
+        <v>545</v>
+      </c>
+      <c r="I30" t="n">
+        <v>555</v>
+      </c>
+      <c r="J30" t="n">
+        <v>564</v>
+      </c>
+      <c r="K30" t="n">
+        <v>574</v>
+      </c>
+      <c r="L30" t="n">
+        <v>584</v>
+      </c>
+      <c r="M30" t="n">
+        <v>593</v>
+      </c>
+      <c r="N30" t="n">
+        <v>603</v>
+      </c>
+      <c r="O30" t="n">
+        <v>612</v>
+      </c>
+      <c r="P30" t="n">
+        <v>622</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>632</v>
+      </c>
+      <c r="R30" t="n">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Client A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>APA-MAA-01</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Seat Ratio</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Client A</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>APA-MAA-01</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Seats Required</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>465.2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>473.9</v>
+      </c>
+      <c r="I32" t="n">
+        <v>482.6</v>
+      </c>
+      <c r="J32" t="n">
+        <v>490.4</v>
+      </c>
+      <c r="K32" t="n">
+        <v>499.1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>507.8</v>
+      </c>
+      <c r="M32" t="n">
+        <v>515.7</v>
+      </c>
+      <c r="N32" t="n">
+        <v>524.3</v>
+      </c>
+      <c r="O32" t="n">
+        <v>532.2</v>
+      </c>
+      <c r="P32" t="n">
+        <v>540.9</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>549.6</v>
+      </c>
+      <c r="R32" t="n">
+        <v>557.4</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Collections</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>APA-MAA-02</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>HC Forecast</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>216</v>
+      </c>
+      <c r="H33" t="n">
+        <v>220</v>
+      </c>
+      <c r="I33" t="n">
+        <v>224</v>
+      </c>
+      <c r="J33" t="n">
+        <v>228</v>
+      </c>
+      <c r="K33" t="n">
+        <v>233</v>
+      </c>
+      <c r="L33" t="n">
+        <v>237</v>
+      </c>
+      <c r="M33" t="n">
+        <v>241</v>
+      </c>
+      <c r="N33" t="n">
+        <v>245</v>
+      </c>
+      <c r="O33" t="n">
+        <v>249</v>
+      </c>
+      <c r="P33" t="n">
+        <v>254</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>258</v>
+      </c>
+      <c r="R33" t="n">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Collections</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>APA-MAA-02</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Seat Ratio</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Collections</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>APA-MAA-02</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Seats Required</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>196.4</v>
+      </c>
+      <c r="H35" t="n">
+        <v>200</v>
+      </c>
+      <c r="I35" t="n">
+        <v>203.6</v>
+      </c>
+      <c r="J35" t="n">
+        <v>207.3</v>
+      </c>
+      <c r="K35" t="n">
+        <v>211.8</v>
+      </c>
+      <c r="L35" t="n">
+        <v>215.5</v>
+      </c>
+      <c r="M35" t="n">
+        <v>219.1</v>
+      </c>
+      <c r="N35" t="n">
+        <v>222.7</v>
+      </c>
+      <c r="O35" t="n">
+        <v>226.4</v>
+      </c>
+      <c r="P35" t="n">
+        <v>230.9</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>234.5</v>
+      </c>
+      <c r="R35" t="n">
+        <v>238.2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>Escalations</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Krakow</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Vistula House</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>APA-MAA-02</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>HC Forecast</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>216</v>
+      </c>
+      <c r="H36" t="n">
+        <v>220</v>
+      </c>
+      <c r="I36" t="n">
+        <v>224</v>
+      </c>
+      <c r="J36" t="n">
+        <v>228</v>
+      </c>
+      <c r="K36" t="n">
+        <v>233</v>
+      </c>
+      <c r="L36" t="n">
+        <v>237</v>
+      </c>
+      <c r="M36" t="n">
+        <v>241</v>
+      </c>
+      <c r="N36" t="n">
+        <v>245</v>
+      </c>
+      <c r="O36" t="n">
+        <v>249</v>
+      </c>
+      <c r="P36" t="n">
+        <v>254</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>258</v>
+      </c>
+      <c r="R36" t="n">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Escalations</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>APA-MAA-02</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Seat Ratio</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Escalations</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>APA-MAA-02</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>Seats Required</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>76</v>
-      </c>
-      <c r="H29" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="I29" t="n">
-        <v>78.40000000000001</v>
-      </c>
-      <c r="J29" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="K29" t="n">
-        <v>80</v>
-      </c>
-      <c r="L29" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="M29" t="n">
-        <v>82.40000000000001</v>
-      </c>
-      <c r="N29" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="O29" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="P29" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="R29" t="n">
-        <v>88</v>
+      <c r="G38" t="n">
+        <v>196.4</v>
+      </c>
+      <c r="H38" t="n">
+        <v>200</v>
+      </c>
+      <c r="I38" t="n">
+        <v>203.6</v>
+      </c>
+      <c r="J38" t="n">
+        <v>207.3</v>
+      </c>
+      <c r="K38" t="n">
+        <v>211.8</v>
+      </c>
+      <c r="L38" t="n">
+        <v>215.5</v>
+      </c>
+      <c r="M38" t="n">
+        <v>219.1</v>
+      </c>
+      <c r="N38" t="n">
+        <v>222.7</v>
+      </c>
+      <c r="O38" t="n">
+        <v>226.4</v>
+      </c>
+      <c r="P38" t="n">
+        <v>230.9</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>234.5</v>
+      </c>
+      <c r="R38" t="n">
+        <v>238.2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Client A</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Customer Care</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>APA-MAA-03</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>HC Forecast</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>388</v>
+      </c>
+      <c r="H39" t="n">
+        <v>394</v>
+      </c>
+      <c r="I39" t="n">
+        <v>400</v>
+      </c>
+      <c r="J39" t="n">
+        <v>406</v>
+      </c>
+      <c r="K39" t="n">
+        <v>413</v>
+      </c>
+      <c r="L39" t="n">
+        <v>419</v>
+      </c>
+      <c r="M39" t="n">
+        <v>425</v>
+      </c>
+      <c r="N39" t="n">
+        <v>431</v>
+      </c>
+      <c r="O39" t="n">
+        <v>437</v>
+      </c>
+      <c r="P39" t="n">
+        <v>443</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>450</v>
+      </c>
+      <c r="R39" t="n">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Client A</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Customer Care</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>APA-MAA-03</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Seat Ratio</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Client A</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Customer Care</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>APA-MAA-03</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Seats Required</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>337.4</v>
+      </c>
+      <c r="H41" t="n">
+        <v>342.6</v>
+      </c>
+      <c r="I41" t="n">
+        <v>347.8</v>
+      </c>
+      <c r="J41" t="n">
+        <v>353</v>
+      </c>
+      <c r="K41" t="n">
+        <v>359.1</v>
+      </c>
+      <c r="L41" t="n">
+        <v>364.3</v>
+      </c>
+      <c r="M41" t="n">
+        <v>369.6</v>
+      </c>
+      <c r="N41" t="n">
+        <v>374.8</v>
+      </c>
+      <c r="O41" t="n">
+        <v>380</v>
+      </c>
+      <c r="P41" t="n">
+        <v>385.2</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>391.3</v>
+      </c>
+      <c r="R41" t="n">
+        <v>396.5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Collections</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>APA-MAA-03</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>HC Forecast</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>227</v>
+      </c>
+      <c r="H42" t="n">
+        <v>231</v>
+      </c>
+      <c r="I42" t="n">
+        <v>235</v>
+      </c>
+      <c r="J42" t="n">
+        <v>238</v>
+      </c>
+      <c r="K42" t="n">
+        <v>242</v>
+      </c>
+      <c r="L42" t="n">
+        <v>246</v>
+      </c>
+      <c r="M42" t="n">
+        <v>249</v>
+      </c>
+      <c r="N42" t="n">
+        <v>253</v>
+      </c>
+      <c r="O42" t="n">
+        <v>256</v>
+      </c>
+      <c r="P42" t="n">
+        <v>260</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>264</v>
+      </c>
+      <c r="R42" t="n">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Collections</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>APA-MAA-03</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Seat Ratio</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Collections</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>APA-MAA-03</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Seats Required</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>206.4</v>
+      </c>
+      <c r="H44" t="n">
+        <v>210</v>
+      </c>
+      <c r="I44" t="n">
+        <v>213.6</v>
+      </c>
+      <c r="J44" t="n">
+        <v>216.4</v>
+      </c>
+      <c r="K44" t="n">
+        <v>220</v>
+      </c>
+      <c r="L44" t="n">
+        <v>223.6</v>
+      </c>
+      <c r="M44" t="n">
+        <v>226.4</v>
+      </c>
+      <c r="N44" t="n">
+        <v>230</v>
+      </c>
+      <c r="O44" t="n">
+        <v>232.7</v>
+      </c>
+      <c r="P44" t="n">
+        <v>236.4</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>240</v>
+      </c>
+      <c r="R44" t="n">
+        <v>242.7</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Client B</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Tech Support</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>EME-BUC-01</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>HC Forecast</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>540</v>
+      </c>
+      <c r="H45" t="n">
+        <v>549</v>
+      </c>
+      <c r="I45" t="n">
+        <v>558</v>
+      </c>
+      <c r="J45" t="n">
+        <v>568</v>
+      </c>
+      <c r="K45" t="n">
+        <v>577</v>
+      </c>
+      <c r="L45" t="n">
+        <v>586</v>
+      </c>
+      <c r="M45" t="n">
+        <v>595</v>
+      </c>
+      <c r="N45" t="n">
+        <v>604</v>
+      </c>
+      <c r="O45" t="n">
+        <v>613</v>
+      </c>
+      <c r="P45" t="n">
+        <v>623</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>632</v>
+      </c>
+      <c r="R45" t="n">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Client B</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Tech Support</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>EME-BUC-01</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Seat Ratio</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Client B</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Tech Support</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>EME-BUC-01</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Seats Required</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>432</v>
+      </c>
+      <c r="H47" t="n">
+        <v>439.2</v>
+      </c>
+      <c r="I47" t="n">
+        <v>446.4</v>
+      </c>
+      <c r="J47" t="n">
+        <v>454.4</v>
+      </c>
+      <c r="K47" t="n">
+        <v>461.6</v>
+      </c>
+      <c r="L47" t="n">
+        <v>468.8</v>
+      </c>
+      <c r="M47" t="n">
+        <v>476</v>
+      </c>
+      <c r="N47" t="n">
+        <v>483.2</v>
+      </c>
+      <c r="O47" t="n">
+        <v>490.4</v>
+      </c>
+      <c r="P47" t="n">
+        <v>498.4</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>505.6</v>
+      </c>
+      <c r="R47" t="n">
+        <v>512.8</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Client B</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Back Office</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>EME-BUC-01</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>HC Forecast</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>540</v>
+      </c>
+      <c r="H48" t="n">
+        <v>549</v>
+      </c>
+      <c r="I48" t="n">
+        <v>558</v>
+      </c>
+      <c r="J48" t="n">
+        <v>568</v>
+      </c>
+      <c r="K48" t="n">
+        <v>577</v>
+      </c>
+      <c r="L48" t="n">
+        <v>586</v>
+      </c>
+      <c r="M48" t="n">
+        <v>595</v>
+      </c>
+      <c r="N48" t="n">
+        <v>604</v>
+      </c>
+      <c r="O48" t="n">
+        <v>613</v>
+      </c>
+      <c r="P48" t="n">
+        <v>623</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>632</v>
+      </c>
+      <c r="R48" t="n">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Client B</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Back Office</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>EME-BUC-01</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Seat Ratio</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Client B</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Back Office</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>EME-BUC-01</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Seats Required</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>432</v>
+      </c>
+      <c r="H50" t="n">
+        <v>439.2</v>
+      </c>
+      <c r="I50" t="n">
+        <v>446.4</v>
+      </c>
+      <c r="J50" t="n">
+        <v>454.4</v>
+      </c>
+      <c r="K50" t="n">
+        <v>461.6</v>
+      </c>
+      <c r="L50" t="n">
+        <v>468.8</v>
+      </c>
+      <c r="M50" t="n">
+        <v>476</v>
+      </c>
+      <c r="N50" t="n">
+        <v>483.2</v>
+      </c>
+      <c r="O50" t="n">
+        <v>490.4</v>
+      </c>
+      <c r="P50" t="n">
+        <v>498.4</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>505.6</v>
+      </c>
+      <c r="R50" t="n">
+        <v>512.8</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Client B</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Tech Support</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>EME-BUC-02</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>HC Forecast</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>258</v>
+      </c>
+      <c r="H51" t="n">
+        <v>262</v>
+      </c>
+      <c r="I51" t="n">
+        <v>265</v>
+      </c>
+      <c r="J51" t="n">
+        <v>268</v>
+      </c>
+      <c r="K51" t="n">
+        <v>272</v>
+      </c>
+      <c r="L51" t="n">
+        <v>275</v>
+      </c>
+      <c r="M51" t="n">
+        <v>279</v>
+      </c>
+      <c r="N51" t="n">
+        <v>282</v>
+      </c>
+      <c r="O51" t="n">
+        <v>286</v>
+      </c>
+      <c r="P51" t="n">
+        <v>289</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>293</v>
+      </c>
+      <c r="R51" t="n">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Client B</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Tech Support</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>EME-BUC-02</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Seat Ratio</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L52" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N52" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P52" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Client B</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Tech Support</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>EME-BUC-02</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Seats Required</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>206.4</v>
+      </c>
+      <c r="H53" t="n">
+        <v>209.6</v>
+      </c>
+      <c r="I53" t="n">
+        <v>212</v>
+      </c>
+      <c r="J53" t="n">
+        <v>214.4</v>
+      </c>
+      <c r="K53" t="n">
+        <v>217.6</v>
+      </c>
+      <c r="L53" t="n">
+        <v>220</v>
+      </c>
+      <c r="M53" t="n">
+        <v>223.2</v>
+      </c>
+      <c r="N53" t="n">
+        <v>225.6</v>
+      </c>
+      <c r="O53" t="n">
+        <v>228.8</v>
+      </c>
+      <c r="P53" t="n">
+        <v>231.2</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>234.4</v>
+      </c>
+      <c r="R53" t="n">
+        <v>236.8</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Collections</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>EME-BUC-02</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>HC Forecast</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>139</v>
+      </c>
+      <c r="H54" t="n">
+        <v>141</v>
+      </c>
+      <c r="I54" t="n">
+        <v>143</v>
+      </c>
+      <c r="J54" t="n">
+        <v>145</v>
+      </c>
+      <c r="K54" t="n">
+        <v>147</v>
+      </c>
+      <c r="L54" t="n">
+        <v>149</v>
+      </c>
+      <c r="M54" t="n">
+        <v>150</v>
+      </c>
+      <c r="N54" t="n">
+        <v>152</v>
+      </c>
+      <c r="O54" t="n">
+        <v>154</v>
+      </c>
+      <c r="P54" t="n">
+        <v>156</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>158</v>
+      </c>
+      <c r="R54" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Collections</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>EME-BUC-02</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Seat Ratio</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L55" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N55" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O55" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P55" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Collections</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>EME-BUC-02</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Seats Required</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>126.4</v>
+      </c>
+      <c r="H56" t="n">
+        <v>128.2</v>
+      </c>
+      <c r="I56" t="n">
+        <v>130</v>
+      </c>
+      <c r="J56" t="n">
+        <v>131.8</v>
+      </c>
+      <c r="K56" t="n">
+        <v>133.6</v>
+      </c>
+      <c r="L56" t="n">
+        <v>135.5</v>
+      </c>
+      <c r="M56" t="n">
+        <v>136.4</v>
+      </c>
+      <c r="N56" t="n">
+        <v>138.2</v>
+      </c>
+      <c r="O56" t="n">
+        <v>140</v>
+      </c>
+      <c r="P56" t="n">
+        <v>141.8</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>143.6</v>
+      </c>
+      <c r="R56" t="n">
+        <v>145.5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Client A</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Customer Care</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>EME-LIS-01</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>HC Forecast</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>352</v>
+      </c>
+      <c r="H57" t="n">
+        <v>357</v>
+      </c>
+      <c r="I57" t="n">
+        <v>363</v>
+      </c>
+      <c r="J57" t="n">
+        <v>368</v>
+      </c>
+      <c r="K57" t="n">
+        <v>374</v>
+      </c>
+      <c r="L57" t="n">
+        <v>380</v>
+      </c>
+      <c r="M57" t="n">
+        <v>385</v>
+      </c>
+      <c r="N57" t="n">
+        <v>391</v>
+      </c>
+      <c r="O57" t="n">
+        <v>396</v>
+      </c>
+      <c r="P57" t="n">
+        <v>402</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>408</v>
+      </c>
+      <c r="R57" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Client A</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Customer Care</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>EME-LIS-01</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Seat Ratio</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N58" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P58" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Client A</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Customer Care</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>EME-LIS-01</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Seats Required</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>306.1</v>
+      </c>
+      <c r="H59" t="n">
+        <v>310.4</v>
+      </c>
+      <c r="I59" t="n">
+        <v>315.7</v>
+      </c>
+      <c r="J59" t="n">
+        <v>320</v>
+      </c>
+      <c r="K59" t="n">
+        <v>325.2</v>
+      </c>
+      <c r="L59" t="n">
+        <v>330.4</v>
+      </c>
+      <c r="M59" t="n">
+        <v>334.8</v>
+      </c>
+      <c r="N59" t="n">
+        <v>340</v>
+      </c>
+      <c r="O59" t="n">
+        <v>344.3</v>
+      </c>
+      <c r="P59" t="n">
+        <v>349.6</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>354.8</v>
+      </c>
+      <c r="R59" t="n">
+        <v>359.1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Collections</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>EME-LIS-01</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>HC Forecast</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>206</v>
+      </c>
+      <c r="H60" t="n">
+        <v>209</v>
+      </c>
+      <c r="I60" t="n">
+        <v>213</v>
+      </c>
+      <c r="J60" t="n">
+        <v>216</v>
+      </c>
+      <c r="K60" t="n">
+        <v>219</v>
+      </c>
+      <c r="L60" t="n">
+        <v>222</v>
+      </c>
+      <c r="M60" t="n">
+        <v>226</v>
+      </c>
+      <c r="N60" t="n">
+        <v>229</v>
+      </c>
+      <c r="O60" t="n">
+        <v>232</v>
+      </c>
+      <c r="P60" t="n">
+        <v>236</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>239</v>
+      </c>
+      <c r="R60" t="n">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Collections</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>EME-LIS-01</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Seat Ratio</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N61" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O61" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P61" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Collections</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>EME-LIS-01</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Seats Required</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>187.3</v>
+      </c>
+      <c r="H62" t="n">
+        <v>190</v>
+      </c>
+      <c r="I62" t="n">
+        <v>193.6</v>
+      </c>
+      <c r="J62" t="n">
+        <v>196.4</v>
+      </c>
+      <c r="K62" t="n">
+        <v>199.1</v>
+      </c>
+      <c r="L62" t="n">
+        <v>201.8</v>
+      </c>
+      <c r="M62" t="n">
+        <v>205.5</v>
+      </c>
+      <c r="N62" t="n">
+        <v>208.2</v>
+      </c>
+      <c r="O62" t="n">
+        <v>210.9</v>
+      </c>
+      <c r="P62" t="n">
+        <v>214.5</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>217.3</v>
+      </c>
+      <c r="R62" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Collections</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>EME-LIS-02</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>HC Forecast</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>223</v>
+      </c>
+      <c r="H63" t="n">
+        <v>224</v>
+      </c>
+      <c r="I63" t="n">
+        <v>226</v>
+      </c>
+      <c r="J63" t="n">
+        <v>227</v>
+      </c>
+      <c r="K63" t="n">
+        <v>228</v>
+      </c>
+      <c r="L63" t="n">
+        <v>229</v>
+      </c>
+      <c r="M63" t="n">
+        <v>230</v>
+      </c>
+      <c r="N63" t="n">
+        <v>231</v>
+      </c>
+      <c r="O63" t="n">
+        <v>232</v>
+      </c>
+      <c r="P63" t="n">
+        <v>233</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>234</v>
+      </c>
+      <c r="R63" t="n">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Collections</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>EME-LIS-02</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Seat Ratio</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L64" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N64" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O64" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Collections</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>EME-LIS-02</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Seats Required</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>202.7</v>
+      </c>
+      <c r="H65" t="n">
+        <v>203.6</v>
+      </c>
+      <c r="I65" t="n">
+        <v>205.5</v>
+      </c>
+      <c r="J65" t="n">
+        <v>206.4</v>
+      </c>
+      <c r="K65" t="n">
+        <v>207.3</v>
+      </c>
+      <c r="L65" t="n">
+        <v>208.2</v>
+      </c>
+      <c r="M65" t="n">
+        <v>209.1</v>
+      </c>
+      <c r="N65" t="n">
+        <v>210</v>
+      </c>
+      <c r="O65" t="n">
+        <v>210.9</v>
+      </c>
+      <c r="P65" t="n">
+        <v>211.8</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>212.7</v>
+      </c>
+      <c r="R65" t="n">
+        <v>214.5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Escalations</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>EME-LIS-02</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>HC Forecast</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>223</v>
+      </c>
+      <c r="H66" t="n">
+        <v>224</v>
+      </c>
+      <c r="I66" t="n">
+        <v>226</v>
+      </c>
+      <c r="J66" t="n">
+        <v>227</v>
+      </c>
+      <c r="K66" t="n">
+        <v>228</v>
+      </c>
+      <c r="L66" t="n">
+        <v>229</v>
+      </c>
+      <c r="M66" t="n">
+        <v>230</v>
+      </c>
+      <c r="N66" t="n">
+        <v>231</v>
+      </c>
+      <c r="O66" t="n">
+        <v>232</v>
+      </c>
+      <c r="P66" t="n">
+        <v>233</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>234</v>
+      </c>
+      <c r="R66" t="n">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Escalations</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>EME-LIS-02</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Seat Ratio</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L67" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N67" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O67" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P67" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Escalations</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>EME-LIS-02</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Seats Required</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>202.7</v>
+      </c>
+      <c r="H68" t="n">
+        <v>203.6</v>
+      </c>
+      <c r="I68" t="n">
+        <v>205.5</v>
+      </c>
+      <c r="J68" t="n">
+        <v>206.4</v>
+      </c>
+      <c r="K68" t="n">
+        <v>207.3</v>
+      </c>
+      <c r="L68" t="n">
+        <v>208.2</v>
+      </c>
+      <c r="M68" t="n">
+        <v>209.1</v>
+      </c>
+      <c r="N68" t="n">
+        <v>210</v>
+      </c>
+      <c r="O68" t="n">
+        <v>210.9</v>
+      </c>
+      <c r="P68" t="n">
+        <v>211.8</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>212.7</v>
+      </c>
+      <c r="R68" t="n">
+        <v>214.5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Client A</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Customer Care</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>EME-CAI-01</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>HC Forecast</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>519</v>
+      </c>
+      <c r="H69" t="n">
+        <v>535</v>
+      </c>
+      <c r="I69" t="n">
+        <v>552</v>
+      </c>
+      <c r="J69" t="n">
+        <v>568</v>
+      </c>
+      <c r="K69" t="n">
+        <v>585</v>
+      </c>
+      <c r="L69" t="n">
+        <v>602</v>
+      </c>
+      <c r="M69" t="n">
+        <v>618</v>
+      </c>
+      <c r="N69" t="n">
+        <v>635</v>
+      </c>
+      <c r="O69" t="n">
+        <v>651</v>
+      </c>
+      <c r="P69" t="n">
+        <v>668</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>685</v>
+      </c>
+      <c r="R69" t="n">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Client A</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Customer Care</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>EME-CAI-01</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Seat Ratio</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J70" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L70" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N70" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O70" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P70" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R70" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Client A</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Customer Care</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>EME-CAI-01</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Seats Required</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>451.3</v>
+      </c>
+      <c r="H71" t="n">
+        <v>465.2</v>
+      </c>
+      <c r="I71" t="n">
+        <v>480</v>
+      </c>
+      <c r="J71" t="n">
+        <v>493.9</v>
+      </c>
+      <c r="K71" t="n">
+        <v>508.7</v>
+      </c>
+      <c r="L71" t="n">
+        <v>523.5</v>
+      </c>
+      <c r="M71" t="n">
+        <v>537.4</v>
+      </c>
+      <c r="N71" t="n">
+        <v>552.2</v>
+      </c>
+      <c r="O71" t="n">
+        <v>566.1</v>
+      </c>
+      <c r="P71" t="n">
+        <v>580.9</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>595.7</v>
+      </c>
+      <c r="R71" t="n">
+        <v>609.6</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Client A</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>EME-CAI-01</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>HC Forecast</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>519</v>
+      </c>
+      <c r="H72" t="n">
+        <v>535</v>
+      </c>
+      <c r="I72" t="n">
+        <v>552</v>
+      </c>
+      <c r="J72" t="n">
+        <v>568</v>
+      </c>
+      <c r="K72" t="n">
+        <v>585</v>
+      </c>
+      <c r="L72" t="n">
+        <v>602</v>
+      </c>
+      <c r="M72" t="n">
+        <v>618</v>
+      </c>
+      <c r="N72" t="n">
+        <v>635</v>
+      </c>
+      <c r="O72" t="n">
+        <v>651</v>
+      </c>
+      <c r="P72" t="n">
+        <v>668</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>685</v>
+      </c>
+      <c r="R72" t="n">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Client A</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>EME-CAI-01</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Seat Ratio</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H73" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I73" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L73" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N73" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O73" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P73" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R73" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Client A</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>EME-CAI-01</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Seats Required</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>451.3</v>
+      </c>
+      <c r="H74" t="n">
+        <v>465.2</v>
+      </c>
+      <c r="I74" t="n">
+        <v>480</v>
+      </c>
+      <c r="J74" t="n">
+        <v>493.9</v>
+      </c>
+      <c r="K74" t="n">
+        <v>508.7</v>
+      </c>
+      <c r="L74" t="n">
+        <v>523.5</v>
+      </c>
+      <c r="M74" t="n">
+        <v>537.4</v>
+      </c>
+      <c r="N74" t="n">
+        <v>552.2</v>
+      </c>
+      <c r="O74" t="n">
+        <v>566.1</v>
+      </c>
+      <c r="P74" t="n">
+        <v>580.9</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>595.7</v>
+      </c>
+      <c r="R74" t="n">
+        <v>609.6</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Client B</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Tech Support</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>EME-CAI-02</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>HC Forecast</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>254</v>
+      </c>
+      <c r="H75" t="n">
+        <v>259</v>
+      </c>
+      <c r="I75" t="n">
+        <v>264</v>
+      </c>
+      <c r="J75" t="n">
+        <v>268</v>
+      </c>
+      <c r="K75" t="n">
+        <v>273</v>
+      </c>
+      <c r="L75" t="n">
+        <v>277</v>
+      </c>
+      <c r="M75" t="n">
+        <v>282</v>
+      </c>
+      <c r="N75" t="n">
+        <v>286</v>
+      </c>
+      <c r="O75" t="n">
+        <v>291</v>
+      </c>
+      <c r="P75" t="n">
+        <v>296</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>300</v>
+      </c>
+      <c r="R75" t="n">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Client B</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Tech Support</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>EME-CAI-02</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Seat Ratio</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J76" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K76" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L76" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N76" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O76" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P76" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Client B</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Tech Support</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>EME-CAI-02</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Seats Required</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>203.2</v>
+      </c>
+      <c r="H77" t="n">
+        <v>207.2</v>
+      </c>
+      <c r="I77" t="n">
+        <v>211.2</v>
+      </c>
+      <c r="J77" t="n">
+        <v>214.4</v>
+      </c>
+      <c r="K77" t="n">
+        <v>218.4</v>
+      </c>
+      <c r="L77" t="n">
+        <v>221.6</v>
+      </c>
+      <c r="M77" t="n">
+        <v>225.6</v>
+      </c>
+      <c r="N77" t="n">
+        <v>228.8</v>
+      </c>
+      <c r="O77" t="n">
+        <v>232.8</v>
+      </c>
+      <c r="P77" t="n">
+        <v>236.8</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>240</v>
+      </c>
+      <c r="R77" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Client B</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Back Office</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>EME-CAI-02</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>HC Forecast</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>254</v>
+      </c>
+      <c r="H78" t="n">
+        <v>259</v>
+      </c>
+      <c r="I78" t="n">
+        <v>264</v>
+      </c>
+      <c r="J78" t="n">
+        <v>268</v>
+      </c>
+      <c r="K78" t="n">
+        <v>273</v>
+      </c>
+      <c r="L78" t="n">
+        <v>277</v>
+      </c>
+      <c r="M78" t="n">
+        <v>282</v>
+      </c>
+      <c r="N78" t="n">
+        <v>286</v>
+      </c>
+      <c r="O78" t="n">
+        <v>291</v>
+      </c>
+      <c r="P78" t="n">
+        <v>296</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>300</v>
+      </c>
+      <c r="R78" t="n">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Client B</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Back Office</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>EME-CAI-02</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Seat Ratio</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H79" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I79" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L79" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N79" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O79" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P79" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R79" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Client B</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Back Office</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>EME-CAI-02</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Seats Required</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>203.2</v>
+      </c>
+      <c r="H80" t="n">
+        <v>207.2</v>
+      </c>
+      <c r="I80" t="n">
+        <v>211.2</v>
+      </c>
+      <c r="J80" t="n">
+        <v>214.4</v>
+      </c>
+      <c r="K80" t="n">
+        <v>218.4</v>
+      </c>
+      <c r="L80" t="n">
+        <v>221.6</v>
+      </c>
+      <c r="M80" t="n">
+        <v>225.6</v>
+      </c>
+      <c r="N80" t="n">
+        <v>228.8</v>
+      </c>
+      <c r="O80" t="n">
+        <v>232.8</v>
+      </c>
+      <c r="P80" t="n">
+        <v>236.8</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>240</v>
+      </c>
+      <c r="R80" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Client A</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Customer Care</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>EME-CAI-03</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>HC Forecast</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>380</v>
+      </c>
+      <c r="H81" t="n">
+        <v>387</v>
+      </c>
+      <c r="I81" t="n">
+        <v>394</v>
+      </c>
+      <c r="J81" t="n">
+        <v>402</v>
+      </c>
+      <c r="K81" t="n">
+        <v>409</v>
+      </c>
+      <c r="L81" t="n">
+        <v>416</v>
+      </c>
+      <c r="M81" t="n">
+        <v>423</v>
+      </c>
+      <c r="N81" t="n">
+        <v>430</v>
+      </c>
+      <c r="O81" t="n">
+        <v>437</v>
+      </c>
+      <c r="P81" t="n">
+        <v>445</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>452</v>
+      </c>
+      <c r="R81" t="n">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Client A</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Customer Care</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>EME-CAI-03</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Seat Ratio</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I82" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J82" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="K82" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L82" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M82" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N82" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O82" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P82" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R82" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Client A</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Customer Care</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>EME-CAI-03</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Seats Required</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>330.4</v>
+      </c>
+      <c r="H83" t="n">
+        <v>336.5</v>
+      </c>
+      <c r="I83" t="n">
+        <v>342.6</v>
+      </c>
+      <c r="J83" t="n">
+        <v>349.6</v>
+      </c>
+      <c r="K83" t="n">
+        <v>355.7</v>
+      </c>
+      <c r="L83" t="n">
+        <v>361.7</v>
+      </c>
+      <c r="M83" t="n">
+        <v>367.8</v>
+      </c>
+      <c r="N83" t="n">
+        <v>373.9</v>
+      </c>
+      <c r="O83" t="n">
+        <v>380</v>
+      </c>
+      <c r="P83" t="n">
+        <v>387</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>393</v>
+      </c>
+      <c r="R83" t="n">
+        <v>399.1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Client B</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Tech Support</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>EME-CAI-03</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>HC Forecast</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>253</v>
+      </c>
+      <c r="H84" t="n">
+        <v>258</v>
+      </c>
+      <c r="I84" t="n">
+        <v>263</v>
+      </c>
+      <c r="J84" t="n">
+        <v>268</v>
+      </c>
+      <c r="K84" t="n">
+        <v>272</v>
+      </c>
+      <c r="L84" t="n">
+        <v>277</v>
+      </c>
+      <c r="M84" t="n">
+        <v>282</v>
+      </c>
+      <c r="N84" t="n">
+        <v>287</v>
+      </c>
+      <c r="O84" t="n">
+        <v>291</v>
+      </c>
+      <c r="P84" t="n">
+        <v>296</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>301</v>
+      </c>
+      <c r="R84" t="n">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Client B</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Tech Support</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>EME-CAI-03</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Seat Ratio</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H85" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I85" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J85" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K85" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L85" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N85" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O85" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P85" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R85" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Client B</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Tech Support</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>EME-CAI-03</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Seats Required</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>202.4</v>
+      </c>
+      <c r="H86" t="n">
+        <v>206.4</v>
+      </c>
+      <c r="I86" t="n">
+        <v>210.4</v>
+      </c>
+      <c r="J86" t="n">
+        <v>214.4</v>
+      </c>
+      <c r="K86" t="n">
+        <v>217.6</v>
+      </c>
+      <c r="L86" t="n">
+        <v>221.6</v>
+      </c>
+      <c r="M86" t="n">
+        <v>225.6</v>
+      </c>
+      <c r="N86" t="n">
+        <v>229.6</v>
+      </c>
+      <c r="O86" t="n">
+        <v>232.8</v>
+      </c>
+      <c r="P86" t="n">
+        <v>236.8</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>240.8</v>
+      </c>
+      <c r="R86" t="n">
+        <v>244.8</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Collections</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Bogota</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AME-BOG-01</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>HC Forecast</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>455</v>
+      </c>
+      <c r="H87" t="n">
+        <v>462</v>
+      </c>
+      <c r="I87" t="n">
+        <v>469</v>
+      </c>
+      <c r="J87" t="n">
+        <v>476</v>
+      </c>
+      <c r="K87" t="n">
+        <v>483</v>
+      </c>
+      <c r="L87" t="n">
+        <v>490</v>
+      </c>
+      <c r="M87" t="n">
+        <v>498</v>
+      </c>
+      <c r="N87" t="n">
+        <v>505</v>
+      </c>
+      <c r="O87" t="n">
+        <v>512</v>
+      </c>
+      <c r="P87" t="n">
+        <v>519</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>526</v>
+      </c>
+      <c r="R87" t="n">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Collections</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Bogota</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AME-BOG-01</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Seat Ratio</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H88" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I88" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J88" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K88" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L88" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N88" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O88" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P88" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R88" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Collections</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Bogota</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AME-BOG-01</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Seats Required</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>413.6</v>
+      </c>
+      <c r="H89" t="n">
+        <v>420</v>
+      </c>
+      <c r="I89" t="n">
+        <v>426.4</v>
+      </c>
+      <c r="J89" t="n">
+        <v>432.7</v>
+      </c>
+      <c r="K89" t="n">
+        <v>439.1</v>
+      </c>
+      <c r="L89" t="n">
+        <v>445.5</v>
+      </c>
+      <c r="M89" t="n">
+        <v>452.7</v>
+      </c>
+      <c r="N89" t="n">
+        <v>459.1</v>
+      </c>
+      <c r="O89" t="n">
+        <v>465.5</v>
+      </c>
+      <c r="P89" t="n">
+        <v>471.8</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>478.2</v>
+      </c>
+      <c r="R89" t="n">
+        <v>484.5</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Escalations</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Bogota</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AME-BOG-01</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>HC Forecast</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>455</v>
+      </c>
+      <c r="H90" t="n">
+        <v>462</v>
+      </c>
+      <c r="I90" t="n">
+        <v>469</v>
+      </c>
+      <c r="J90" t="n">
+        <v>476</v>
+      </c>
+      <c r="K90" t="n">
+        <v>483</v>
+      </c>
+      <c r="L90" t="n">
+        <v>490</v>
+      </c>
+      <c r="M90" t="n">
+        <v>498</v>
+      </c>
+      <c r="N90" t="n">
+        <v>505</v>
+      </c>
+      <c r="O90" t="n">
+        <v>512</v>
+      </c>
+      <c r="P90" t="n">
+        <v>519</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>526</v>
+      </c>
+      <c r="R90" t="n">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Escalations</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Bogota</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AME-BOG-01</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Seat Ratio</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H91" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I91" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J91" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K91" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L91" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N91" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O91" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P91" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R91" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Escalations</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Bogota</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AME-BOG-01</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Seats Required</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>413.6</v>
+      </c>
+      <c r="H92" t="n">
+        <v>420</v>
+      </c>
+      <c r="I92" t="n">
+        <v>426.4</v>
+      </c>
+      <c r="J92" t="n">
+        <v>432.7</v>
+      </c>
+      <c r="K92" t="n">
+        <v>439.1</v>
+      </c>
+      <c r="L92" t="n">
+        <v>445.5</v>
+      </c>
+      <c r="M92" t="n">
+        <v>452.7</v>
+      </c>
+      <c r="N92" t="n">
+        <v>459.1</v>
+      </c>
+      <c r="O92" t="n">
+        <v>465.5</v>
+      </c>
+      <c r="P92" t="n">
+        <v>471.8</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>478.2</v>
+      </c>
+      <c r="R92" t="n">
+        <v>484.5</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Client A</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Customer Care</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Bogota</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AME-BOG-02</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>HC Forecast</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>147</v>
+      </c>
+      <c r="H93" t="n">
+        <v>149</v>
+      </c>
+      <c r="I93" t="n">
+        <v>151</v>
+      </c>
+      <c r="J93" t="n">
+        <v>154</v>
+      </c>
+      <c r="K93" t="n">
+        <v>156</v>
+      </c>
+      <c r="L93" t="n">
+        <v>158</v>
+      </c>
+      <c r="M93" t="n">
+        <v>160</v>
+      </c>
+      <c r="N93" t="n">
+        <v>163</v>
+      </c>
+      <c r="O93" t="n">
+        <v>165</v>
+      </c>
+      <c r="P93" t="n">
+        <v>167</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>170</v>
+      </c>
+      <c r="R93" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Client A</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Customer Care</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Bogota</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AME-BOG-02</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Seat Ratio</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H94" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I94" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J94" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="K94" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L94" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M94" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N94" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O94" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P94" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R94" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Client A</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Customer Care</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Bogota</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AME-BOG-02</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Seats Required</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>127.8</v>
+      </c>
+      <c r="H95" t="n">
+        <v>129.6</v>
+      </c>
+      <c r="I95" t="n">
+        <v>131.3</v>
+      </c>
+      <c r="J95" t="n">
+        <v>133.9</v>
+      </c>
+      <c r="K95" t="n">
+        <v>135.7</v>
+      </c>
+      <c r="L95" t="n">
+        <v>137.4</v>
+      </c>
+      <c r="M95" t="n">
+        <v>139.1</v>
+      </c>
+      <c r="N95" t="n">
+        <v>141.7</v>
+      </c>
+      <c r="O95" t="n">
+        <v>143.5</v>
+      </c>
+      <c r="P95" t="n">
+        <v>145.2</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>147.8</v>
+      </c>
+      <c r="R95" t="n">
+        <v>149.6</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Client A</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Bogota</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AME-BOG-02</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>HC Forecast</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>147</v>
+      </c>
+      <c r="H96" t="n">
+        <v>149</v>
+      </c>
+      <c r="I96" t="n">
+        <v>151</v>
+      </c>
+      <c r="J96" t="n">
+        <v>154</v>
+      </c>
+      <c r="K96" t="n">
+        <v>156</v>
+      </c>
+      <c r="L96" t="n">
+        <v>158</v>
+      </c>
+      <c r="M96" t="n">
+        <v>160</v>
+      </c>
+      <c r="N96" t="n">
+        <v>163</v>
+      </c>
+      <c r="O96" t="n">
+        <v>165</v>
+      </c>
+      <c r="P96" t="n">
+        <v>167</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>170</v>
+      </c>
+      <c r="R96" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Client A</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Bogota</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AME-BOG-02</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Seat Ratio</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H97" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I97" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J97" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L97" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M97" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N97" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O97" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P97" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R97" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Client A</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Bogota</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AME-BOG-02</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Seats Required</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>127.8</v>
+      </c>
+      <c r="H98" t="n">
+        <v>129.6</v>
+      </c>
+      <c r="I98" t="n">
+        <v>131.3</v>
+      </c>
+      <c r="J98" t="n">
+        <v>133.9</v>
+      </c>
+      <c r="K98" t="n">
+        <v>135.7</v>
+      </c>
+      <c r="L98" t="n">
+        <v>137.4</v>
+      </c>
+      <c r="M98" t="n">
+        <v>139.1</v>
+      </c>
+      <c r="N98" t="n">
+        <v>141.7</v>
+      </c>
+      <c r="O98" t="n">
+        <v>143.5</v>
+      </c>
+      <c r="P98" t="n">
+        <v>145.2</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>147.8</v>
+      </c>
+      <c r="R98" t="n">
+        <v>149.6</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Client B</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Tech Support</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Guadalajara</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AME-GDL-01</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>HC Forecast</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>280</v>
+      </c>
+      <c r="H99" t="n">
+        <v>285</v>
+      </c>
+      <c r="I99" t="n">
+        <v>289</v>
+      </c>
+      <c r="J99" t="n">
+        <v>294</v>
+      </c>
+      <c r="K99" t="n">
+        <v>299</v>
+      </c>
+      <c r="L99" t="n">
+        <v>303</v>
+      </c>
+      <c r="M99" t="n">
+        <v>308</v>
+      </c>
+      <c r="N99" t="n">
+        <v>313</v>
+      </c>
+      <c r="O99" t="n">
+        <v>318</v>
+      </c>
+      <c r="P99" t="n">
+        <v>322</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>327</v>
+      </c>
+      <c r="R99" t="n">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Client B</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Tech Support</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Guadalajara</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AME-GDL-01</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Seat Ratio</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H100" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I100" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J100" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K100" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L100" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M100" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N100" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O100" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P100" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R100" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Client B</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Tech Support</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Guadalajara</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AME-GDL-01</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Seats Required</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>224</v>
+      </c>
+      <c r="H101" t="n">
+        <v>228</v>
+      </c>
+      <c r="I101" t="n">
+        <v>231.2</v>
+      </c>
+      <c r="J101" t="n">
+        <v>235.2</v>
+      </c>
+      <c r="K101" t="n">
+        <v>239.2</v>
+      </c>
+      <c r="L101" t="n">
+        <v>242.4</v>
+      </c>
+      <c r="M101" t="n">
+        <v>246.4</v>
+      </c>
+      <c r="N101" t="n">
+        <v>250.4</v>
+      </c>
+      <c r="O101" t="n">
+        <v>254.4</v>
+      </c>
+      <c r="P101" t="n">
+        <v>257.6</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>261.6</v>
+      </c>
+      <c r="R101" t="n">
+        <v>265.6</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Client B</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Back Office</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Guadalajara</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AME-GDL-01</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>HC Forecast</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>280</v>
+      </c>
+      <c r="H102" t="n">
+        <v>285</v>
+      </c>
+      <c r="I102" t="n">
+        <v>289</v>
+      </c>
+      <c r="J102" t="n">
+        <v>294</v>
+      </c>
+      <c r="K102" t="n">
+        <v>299</v>
+      </c>
+      <c r="L102" t="n">
+        <v>303</v>
+      </c>
+      <c r="M102" t="n">
+        <v>308</v>
+      </c>
+      <c r="N102" t="n">
+        <v>313</v>
+      </c>
+      <c r="O102" t="n">
+        <v>318</v>
+      </c>
+      <c r="P102" t="n">
+        <v>322</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>327</v>
+      </c>
+      <c r="R102" t="n">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Client B</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Back Office</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Guadalajara</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AME-GDL-01</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Seat Ratio</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H103" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I103" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J103" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K103" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L103" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M103" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N103" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O103" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P103" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R103" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Client B</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Back Office</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Guadalajara</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AME-GDL-01</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Seats Required</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>224</v>
+      </c>
+      <c r="H104" t="n">
+        <v>228</v>
+      </c>
+      <c r="I104" t="n">
+        <v>231.2</v>
+      </c>
+      <c r="J104" t="n">
+        <v>235.2</v>
+      </c>
+      <c r="K104" t="n">
+        <v>239.2</v>
+      </c>
+      <c r="L104" t="n">
+        <v>242.4</v>
+      </c>
+      <c r="M104" t="n">
+        <v>246.4</v>
+      </c>
+      <c r="N104" t="n">
+        <v>250.4</v>
+      </c>
+      <c r="O104" t="n">
+        <v>254.4</v>
+      </c>
+      <c r="P104" t="n">
+        <v>257.6</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>261.6</v>
+      </c>
+      <c r="R104" t="n">
+        <v>265.6</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Client A</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Customer Care</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Guadalajara</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AME-GDL-02</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>HC Forecast</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>318</v>
+      </c>
+      <c r="H105" t="n">
+        <v>320</v>
+      </c>
+      <c r="I105" t="n">
+        <v>322</v>
+      </c>
+      <c r="J105" t="n">
+        <v>324</v>
+      </c>
+      <c r="K105" t="n">
+        <v>326</v>
+      </c>
+      <c r="L105" t="n">
+        <v>328</v>
+      </c>
+      <c r="M105" t="n">
+        <v>329</v>
+      </c>
+      <c r="N105" t="n">
+        <v>331</v>
+      </c>
+      <c r="O105" t="n">
+        <v>333</v>
+      </c>
+      <c r="P105" t="n">
+        <v>335</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>337</v>
+      </c>
+      <c r="R105" t="n">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Client A</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Customer Care</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Guadalajara</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AME-GDL-02</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Seat Ratio</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H106" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I106" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J106" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L106" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M106" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N106" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O106" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P106" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R106" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Client A</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Customer Care</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Guadalajara</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AME-GDL-02</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Seats Required</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>276.5</v>
+      </c>
+      <c r="H107" t="n">
+        <v>278.3</v>
+      </c>
+      <c r="I107" t="n">
+        <v>280</v>
+      </c>
+      <c r="J107" t="n">
+        <v>281.7</v>
+      </c>
+      <c r="K107" t="n">
+        <v>283.5</v>
+      </c>
+      <c r="L107" t="n">
+        <v>285.2</v>
+      </c>
+      <c r="M107" t="n">
+        <v>286.1</v>
+      </c>
+      <c r="N107" t="n">
+        <v>287.8</v>
+      </c>
+      <c r="O107" t="n">
+        <v>289.6</v>
+      </c>
+      <c r="P107" t="n">
+        <v>291.3</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>293</v>
+      </c>
+      <c r="R107" t="n">
+        <v>294.8</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Client B</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Tech Support</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Guadalajara</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AME-GDL-02</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>HC Forecast</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>212</v>
+      </c>
+      <c r="H108" t="n">
+        <v>213</v>
+      </c>
+      <c r="I108" t="n">
+        <v>214</v>
+      </c>
+      <c r="J108" t="n">
+        <v>216</v>
+      </c>
+      <c r="K108" t="n">
+        <v>217</v>
+      </c>
+      <c r="L108" t="n">
+        <v>218</v>
+      </c>
+      <c r="M108" t="n">
+        <v>219</v>
+      </c>
+      <c r="N108" t="n">
+        <v>221</v>
+      </c>
+      <c r="O108" t="n">
+        <v>222</v>
+      </c>
+      <c r="P108" t="n">
+        <v>223</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>225</v>
+      </c>
+      <c r="R108" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Client B</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Tech Support</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Guadalajara</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AME-GDL-02</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Seat Ratio</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H109" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I109" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J109" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K109" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L109" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M109" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N109" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O109" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P109" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R109" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Client B</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Tech Support</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Guadalajara</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AME-GDL-02</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Seats Required</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>169.6</v>
+      </c>
+      <c r="H110" t="n">
+        <v>170.4</v>
+      </c>
+      <c r="I110" t="n">
+        <v>171.2</v>
+      </c>
+      <c r="J110" t="n">
+        <v>172.8</v>
+      </c>
+      <c r="K110" t="n">
+        <v>173.6</v>
+      </c>
+      <c r="L110" t="n">
+        <v>174.4</v>
+      </c>
+      <c r="M110" t="n">
+        <v>175.2</v>
+      </c>
+      <c r="N110" t="n">
+        <v>176.8</v>
+      </c>
+      <c r="O110" t="n">
+        <v>177.6</v>
+      </c>
+      <c r="P110" t="n">
+        <v>178.4</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>180</v>
+      </c>
+      <c r="R110" t="n">
+        <v>180.8</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Collections</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AME-YWG-01</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>HC Forecast</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>476</v>
+      </c>
+      <c r="H111" t="n">
+        <v>490</v>
+      </c>
+      <c r="I111" t="n">
+        <v>505</v>
+      </c>
+      <c r="J111" t="n">
+        <v>520</v>
+      </c>
+      <c r="K111" t="n">
+        <v>535</v>
+      </c>
+      <c r="L111" t="n">
+        <v>549</v>
+      </c>
+      <c r="M111" t="n">
+        <v>564</v>
+      </c>
+      <c r="N111" t="n">
+        <v>579</v>
+      </c>
+      <c r="O111" t="n">
+        <v>594</v>
+      </c>
+      <c r="P111" t="n">
+        <v>608</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>623</v>
+      </c>
+      <c r="R111" t="n">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Collections</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AME-YWG-01</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Seat Ratio</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H112" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I112" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J112" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K112" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L112" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M112" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N112" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O112" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P112" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R112" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Collections</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AME-YWG-01</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Seats Required</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>432.7</v>
+      </c>
+      <c r="H113" t="n">
+        <v>445.5</v>
+      </c>
+      <c r="I113" t="n">
+        <v>459.1</v>
+      </c>
+      <c r="J113" t="n">
+        <v>472.7</v>
+      </c>
+      <c r="K113" t="n">
+        <v>486.4</v>
+      </c>
+      <c r="L113" t="n">
+        <v>499.1</v>
+      </c>
+      <c r="M113" t="n">
+        <v>512.7</v>
+      </c>
+      <c r="N113" t="n">
+        <v>526.4</v>
+      </c>
+      <c r="O113" t="n">
+        <v>540</v>
+      </c>
+      <c r="P113" t="n">
+        <v>552.7</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>566.4</v>
+      </c>
+      <c r="R113" t="n">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Escalations</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AME-YWG-01</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>HC Forecast</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>476</v>
+      </c>
+      <c r="H114" t="n">
+        <v>490</v>
+      </c>
+      <c r="I114" t="n">
+        <v>505</v>
+      </c>
+      <c r="J114" t="n">
+        <v>520</v>
+      </c>
+      <c r="K114" t="n">
+        <v>535</v>
+      </c>
+      <c r="L114" t="n">
+        <v>549</v>
+      </c>
+      <c r="M114" t="n">
+        <v>564</v>
+      </c>
+      <c r="N114" t="n">
+        <v>579</v>
+      </c>
+      <c r="O114" t="n">
+        <v>594</v>
+      </c>
+      <c r="P114" t="n">
+        <v>608</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>623</v>
+      </c>
+      <c r="R114" t="n">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Escalations</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AME-YWG-01</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Seat Ratio</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H115" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I115" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J115" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K115" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L115" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M115" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N115" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O115" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P115" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R115" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Escalations</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AME-YWG-01</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Seats Required</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>432.7</v>
+      </c>
+      <c r="H116" t="n">
+        <v>445.5</v>
+      </c>
+      <c r="I116" t="n">
+        <v>459.1</v>
+      </c>
+      <c r="J116" t="n">
+        <v>472.7</v>
+      </c>
+      <c r="K116" t="n">
+        <v>486.4</v>
+      </c>
+      <c r="L116" t="n">
+        <v>499.1</v>
+      </c>
+      <c r="M116" t="n">
+        <v>512.7</v>
+      </c>
+      <c r="N116" t="n">
+        <v>526.4</v>
+      </c>
+      <c r="O116" t="n">
+        <v>540</v>
+      </c>
+      <c r="P116" t="n">
+        <v>552.7</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>566.4</v>
+      </c>
+      <c r="R116" t="n">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Collections</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AME-YWG-02</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>HC Forecast</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>239</v>
+      </c>
+      <c r="H117" t="n">
+        <v>243</v>
+      </c>
+      <c r="I117" t="n">
+        <v>248</v>
+      </c>
+      <c r="J117" t="n">
+        <v>252</v>
+      </c>
+      <c r="K117" t="n">
+        <v>257</v>
+      </c>
+      <c r="L117" t="n">
+        <v>261</v>
+      </c>
+      <c r="M117" t="n">
+        <v>266</v>
+      </c>
+      <c r="N117" t="n">
+        <v>270</v>
+      </c>
+      <c r="O117" t="n">
+        <v>275</v>
+      </c>
+      <c r="P117" t="n">
+        <v>279</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>283</v>
+      </c>
+      <c r="R117" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Collections</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AME-YWG-02</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Seat Ratio</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H118" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I118" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J118" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K118" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L118" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M118" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N118" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O118" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P118" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R118" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Collections</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AME-YWG-02</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Seats Required</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>217.3</v>
+      </c>
+      <c r="H119" t="n">
+        <v>220.9</v>
+      </c>
+      <c r="I119" t="n">
+        <v>225.5</v>
+      </c>
+      <c r="J119" t="n">
+        <v>229.1</v>
+      </c>
+      <c r="K119" t="n">
+        <v>233.6</v>
+      </c>
+      <c r="L119" t="n">
+        <v>237.3</v>
+      </c>
+      <c r="M119" t="n">
+        <v>241.8</v>
+      </c>
+      <c r="N119" t="n">
+        <v>245.5</v>
+      </c>
+      <c r="O119" t="n">
+        <v>250</v>
+      </c>
+      <c r="P119" t="n">
+        <v>253.6</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>257.3</v>
+      </c>
+      <c r="R119" t="n">
+        <v>261.8</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Client A</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Customer Care</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AME-YWG-02</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>HC Forecast</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>153</v>
+      </c>
+      <c r="H120" t="n">
+        <v>156</v>
+      </c>
+      <c r="I120" t="n">
+        <v>159</v>
+      </c>
+      <c r="J120" t="n">
+        <v>162</v>
+      </c>
+      <c r="K120" t="n">
+        <v>164</v>
+      </c>
+      <c r="L120" t="n">
+        <v>167</v>
+      </c>
+      <c r="M120" t="n">
+        <v>170</v>
+      </c>
+      <c r="N120" t="n">
+        <v>173</v>
+      </c>
+      <c r="O120" t="n">
+        <v>176</v>
+      </c>
+      <c r="P120" t="n">
+        <v>179</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>182</v>
+      </c>
+      <c r="R120" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Client A</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Customer Care</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AME-YWG-02</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Seat Ratio</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H121" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I121" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J121" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="K121" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L121" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M121" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N121" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O121" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P121" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R121" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Client A</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Customer Care</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AME-YWG-02</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Seats Required</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>133</v>
+      </c>
+      <c r="H122" t="n">
+        <v>135.7</v>
+      </c>
+      <c r="I122" t="n">
+        <v>138.3</v>
+      </c>
+      <c r="J122" t="n">
+        <v>140.9</v>
+      </c>
+      <c r="K122" t="n">
+        <v>142.6</v>
+      </c>
+      <c r="L122" t="n">
+        <v>145.2</v>
+      </c>
+      <c r="M122" t="n">
+        <v>147.8</v>
+      </c>
+      <c r="N122" t="n">
+        <v>150.4</v>
+      </c>
+      <c r="O122" t="n">
+        <v>153</v>
+      </c>
+      <c r="P122" t="n">
+        <v>155.7</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>158.3</v>
+      </c>
+      <c r="R122" t="n">
+        <v>160.9</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Client B</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Tech Support</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AME-YWG-03</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>HC Forecast</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>316</v>
+      </c>
+      <c r="H123" t="n">
+        <v>321</v>
+      </c>
+      <c r="I123" t="n">
+        <v>326</v>
+      </c>
+      <c r="J123" t="n">
+        <v>331</v>
+      </c>
+      <c r="K123" t="n">
+        <v>336</v>
+      </c>
+      <c r="L123" t="n">
+        <v>341</v>
+      </c>
+      <c r="M123" t="n">
+        <v>346</v>
+      </c>
+      <c r="N123" t="n">
+        <v>351</v>
+      </c>
+      <c r="O123" t="n">
+        <v>356</v>
+      </c>
+      <c r="P123" t="n">
+        <v>360</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>365</v>
+      </c>
+      <c r="R123" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Client B</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Tech Support</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AME-YWG-03</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Seat Ratio</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H124" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I124" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J124" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K124" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L124" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M124" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N124" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O124" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P124" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R124" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Client B</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Tech Support</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AME-YWG-03</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Seats Required</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>252.8</v>
+      </c>
+      <c r="H125" t="n">
+        <v>256.8</v>
+      </c>
+      <c r="I125" t="n">
+        <v>260.8</v>
+      </c>
+      <c r="J125" t="n">
+        <v>264.8</v>
+      </c>
+      <c r="K125" t="n">
+        <v>268.8</v>
+      </c>
+      <c r="L125" t="n">
+        <v>272.8</v>
+      </c>
+      <c r="M125" t="n">
+        <v>276.8</v>
+      </c>
+      <c r="N125" t="n">
+        <v>280.8</v>
+      </c>
+      <c r="O125" t="n">
+        <v>284.8</v>
+      </c>
+      <c r="P125" t="n">
+        <v>288</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>292</v>
+      </c>
+      <c r="R125" t="n">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Client B</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Back Office</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AME-YWG-03</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>HC Forecast</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>316</v>
+      </c>
+      <c r="H126" t="n">
+        <v>321</v>
+      </c>
+      <c r="I126" t="n">
+        <v>326</v>
+      </c>
+      <c r="J126" t="n">
+        <v>331</v>
+      </c>
+      <c r="K126" t="n">
+        <v>336</v>
+      </c>
+      <c r="L126" t="n">
+        <v>341</v>
+      </c>
+      <c r="M126" t="n">
+        <v>346</v>
+      </c>
+      <c r="N126" t="n">
+        <v>351</v>
+      </c>
+      <c r="O126" t="n">
+        <v>356</v>
+      </c>
+      <c r="P126" t="n">
+        <v>360</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>365</v>
+      </c>
+      <c r="R126" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Client B</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Back Office</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AME-YWG-03</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Seat Ratio</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H127" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I127" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J127" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K127" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L127" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M127" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N127" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O127" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P127" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R127" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Client B</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Back Office</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AME-YWG-03</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Seats Required</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>252.8</v>
+      </c>
+      <c r="H128" t="n">
+        <v>256.8</v>
+      </c>
+      <c r="I128" t="n">
+        <v>260.8</v>
+      </c>
+      <c r="J128" t="n">
+        <v>264.8</v>
+      </c>
+      <c r="K128" t="n">
+        <v>268.8</v>
+      </c>
+      <c r="L128" t="n">
+        <v>272.8</v>
+      </c>
+      <c r="M128" t="n">
+        <v>276.8</v>
+      </c>
+      <c r="N128" t="n">
+        <v>280.8</v>
+      </c>
+      <c r="O128" t="n">
+        <v>284.8</v>
+      </c>
+      <c r="P128" t="n">
+        <v>288</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>292</v>
+      </c>
+      <c r="R128" t="n">
+        <v>296</v>
       </c>
     </row>
   </sheetData>
